--- a/inputs/capex_opex_converted.xlsx
+++ b/inputs/capex_opex_converted.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1091"/>
+  <dimension ref="A1:J1092"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50177,26 +50177,26 @@
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>0.12</v>
+        <v>5.25</v>
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>World</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>BESS</t>
         </is>
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kWh/year</t>
         </is>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t>wacc</t>
+          <t>opex_f</t>
         </is>
       </c>
       <c r="G1082" t="inlineStr">
@@ -50206,17 +50206,15 @@
       </c>
       <c r="H1082" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I1082" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1082" t="n">
+        <v>2025</v>
       </c>
       <c r="J1082" t="inlineStr">
         <is>
-          <t>IRENA 2024</t>
+          <t>Lazard 2024</t>
         </is>
       </c>
     </row>
@@ -50227,11 +50225,11 @@
         </is>
       </c>
       <c r="B1083" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
@@ -50277,11 +50275,11 @@
         </is>
       </c>
       <c r="B1084" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
@@ -50327,11 +50325,11 @@
         </is>
       </c>
       <c r="B1085" t="n">
-        <v>0.055</v>
+        <v>0.042</v>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -50377,11 +50375,11 @@
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>0.077</v>
+        <v>0.055</v>
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
@@ -50427,11 +50425,11 @@
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>0.039</v>
+        <v>0.077</v>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
@@ -50477,31 +50475,31 @@
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>25</v>
+        <v>0.039</v>
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>World</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>wacc</t>
         </is>
       </c>
       <c r="G1088" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>historic</t>
         </is>
       </c>
       <c r="H1088" t="inlineStr">
@@ -50516,7 +50514,7 @@
       </c>
       <c r="J1088" t="inlineStr">
         <is>
-          <t>GNESTE</t>
+          <t>IRENA 2024</t>
         </is>
       </c>
     </row>
@@ -50527,7 +50525,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>0.57</v>
+        <v>25</v>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
@@ -50541,12 +50539,12 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
-          <t>efficiency</t>
+          <t>life</t>
         </is>
       </c>
       <c r="G1089" t="inlineStr">
@@ -50577,7 +50575,7 @@
         </is>
       </c>
       <c r="B1090" t="n">
-        <v>40</v>
+        <v>0.57</v>
       </c>
       <c r="C1090" t="inlineStr">
         <is>
@@ -50586,17 +50584,17 @@
       </c>
       <c r="D1090" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>efficiency</t>
         </is>
       </c>
       <c r="G1090" t="inlineStr">
@@ -50616,7 +50614,7 @@
       </c>
       <c r="J1090" t="inlineStr">
         <is>
-          <t>GNESTE [lazard/ASSET]</t>
+          <t>GNESTE</t>
         </is>
       </c>
     </row>
@@ -50627,44 +50625,94 @@
         </is>
       </c>
       <c r="B1091" t="n">
+        <v>40</v>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>life</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>GNESTE [lazard/ASSET]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
         <v>0.43</v>
       </c>
-      <c r="C1091" t="inlineStr">
+      <c r="C1092" t="inlineStr">
         <is>
           <t>World</t>
         </is>
       </c>
-      <c r="D1091" t="inlineStr">
+      <c r="D1092" t="inlineStr">
         <is>
           <t>Coal</t>
         </is>
       </c>
-      <c r="E1091" t="inlineStr">
+      <c r="E1092" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F1091" t="inlineStr">
+      <c r="F1092" t="inlineStr">
         <is>
           <t>efficiency</t>
         </is>
       </c>
-      <c r="G1091" t="inlineStr">
+      <c r="G1092" t="inlineStr">
         <is>
           <t>projected</t>
         </is>
       </c>
-      <c r="H1091" t="inlineStr">
+      <c r="H1092" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1091" t="inlineStr">
+      <c r="I1092" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1091" t="inlineStr">
+      <c r="J1092" t="inlineStr">
         <is>
           <t>GNESTE</t>
         </is>

--- a/inputs/capex_opex_converted.xlsx
+++ b/inputs/capex_opex_converted.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1092"/>
+  <dimension ref="A1:J1095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50525,7 +50525,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
@@ -50549,7 +50549,7 @@
       </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>historic</t>
         </is>
       </c>
       <c r="H1089" t="inlineStr">
@@ -50564,7 +50564,7 @@
       </c>
       <c r="J1089" t="inlineStr">
         <is>
-          <t>GNESTE</t>
+          <t>Lazard 2025</t>
         </is>
       </c>
     </row>
@@ -50649,7 +50649,7 @@
       </c>
       <c r="G1091" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>historic</t>
         </is>
       </c>
       <c r="H1091" t="inlineStr">
@@ -50664,7 +50664,7 @@
       </c>
       <c r="J1091" t="inlineStr">
         <is>
-          <t>GNESTE [lazard/ASSET]</t>
+          <t>Lazard 2025</t>
         </is>
       </c>
     </row>
@@ -50715,6 +50715,156 @@
       <c r="J1092" t="inlineStr">
         <is>
           <t>GNESTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>life</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J1093" t="inlineStr">
+        <is>
+          <t>Lazard 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>life</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>Lazard 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>70</v>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>life</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>Lazard 2025</t>
         </is>
       </c>
     </row>

--- a/inputs/capex_opex_converted.xlsx
+++ b/inputs/capex_opex_converted.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1095"/>
+  <dimension ref="A1:J1134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50219,650 +50219,2444 @@
       </c>
     </row>
     <row r="1083">
-      <c r="A1083" t="inlineStr">
+      <c r="A1083" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B1083" t="n">
+        <v>12.76140970742</v>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1083" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1083" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B1084" t="n">
+        <v>12.2837098788</v>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1084" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1084" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B1085" t="n">
+        <v>11.19182455624</v>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1085" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B1086" t="n">
+        <v>12.14722421348</v>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1086" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1086" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B1087" t="n">
+        <v>13.3073523687</v>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1087" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1087" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B1088" t="n">
+        <v>12.82965254008</v>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1088" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1088" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B1089" t="n">
+        <v>9.38338949075</v>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1089" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B1090" t="n">
+        <v>11.39655305422</v>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1090" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B1091" t="n">
+        <v>17.87962215692</v>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1091" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B1092" t="n">
+        <v>15.93470142611</v>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1092" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1092" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B1093" t="n">
+        <v>15.11578743419</v>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1093" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1093" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B1094" t="n">
+        <v>16.99246533234</v>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1094" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B1095" t="n">
+        <v>20.09751421837</v>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1095" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B1096" t="n">
+        <v>23.98735567999</v>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1096" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1096" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B1097" t="n">
+        <v>27.46774014565</v>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1097" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1097" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B1098" t="n">
+        <v>28.69611113353</v>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1098" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1098" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B1099" t="n">
+        <v>39.54672152647</v>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1099" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1099" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B1100" t="n">
+        <v>25.55694083117</v>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1100" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1100" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B1101" t="n">
+        <v>32.00588851754</v>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1101" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1101" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B1102" t="n">
+        <v>53.05880239315</v>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1102" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1102" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B1103" t="n">
+        <v>61.89624922262</v>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1103" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1103" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B1104" t="n">
+        <v>59.16653591622</v>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1104" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1104" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B1105" t="n">
+        <v>58.006407761</v>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1105" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1105" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B1106" t="n">
+        <v>37.39707229768</v>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1106" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1106" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B1107" t="n">
+        <v>25.38633374952</v>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1107" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1107" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B1108" t="n">
+        <v>24.73802683925</v>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1108" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B1109" t="n">
+        <v>33.43898800340001</v>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1109" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1109" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B1110" t="n">
+        <v>18.56205048352</v>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1110" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B1111" t="n">
+        <v>14.91105893621</v>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1111" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1111" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B1112" t="n">
+        <v>63.46583437380001</v>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1112" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B1113" t="n">
+        <v>113.6243163789</v>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1113" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B1114" t="n">
+        <v>45.92742638018</v>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1114" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1114" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B1115" t="n">
+        <v>39.95617852243</v>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1115" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B1116" t="n">
+        <v>44.46020547799</v>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1116" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1116" t="inlineStr">
+        <is>
+          <t>FRED [2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1117" t="n">
+        <v>35.69100148118</v>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1117" t="inlineStr">
+        <is>
+          <t>Japan/Korea futures</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B1118" t="n">
+        <v>33.71195933404</v>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1118" t="inlineStr">
+        <is>
+          <t>Japan/Korea futures</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B1119" t="n">
+        <v>31.28933877461</v>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1119" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1119" t="inlineStr">
+        <is>
+          <t>Japan/Korea futures</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B1120" t="n">
+        <v>29.71975362343</v>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1120" t="inlineStr">
+        <is>
+          <t>Japan/Korea futures</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B1121" t="n">
+        <v>27.94543997427</v>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>MWh_th</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I1121" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J1121" t="inlineStr">
+        <is>
+          <t>Japan/Korea futures</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1083" t="n">
+      <c r="B1122" t="n">
         <v>0.12</v>
       </c>
-      <c r="C1083" t="inlineStr">
+      <c r="C1122" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
       </c>
-      <c r="D1083" t="inlineStr">
+      <c r="D1122" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="E1083" t="inlineStr">
+      <c r="E1122" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F1083" t="inlineStr">
+      <c r="F1122" t="inlineStr">
         <is>
           <t>wacc</t>
         </is>
       </c>
-      <c r="G1083" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
-      <c r="H1083" t="inlineStr">
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1083" t="inlineStr">
+      <c r="I1122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1083" t="inlineStr">
+      <c r="J1122" t="inlineStr">
         <is>
           <t>IRENA 2024</t>
         </is>
       </c>
     </row>
-    <row r="1084">
-      <c r="A1084" t="inlineStr">
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1084" t="n">
+      <c r="B1123" t="n">
         <v>0.04</v>
       </c>
-      <c r="C1084" t="inlineStr">
+      <c r="C1123" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="D1084" t="inlineStr">
+      <c r="D1123" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="E1084" t="inlineStr">
+      <c r="E1123" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F1084" t="inlineStr">
+      <c r="F1123" t="inlineStr">
         <is>
           <t>wacc</t>
         </is>
       </c>
-      <c r="G1084" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
-      <c r="H1084" t="inlineStr">
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1084" t="inlineStr">
+      <c r="I1123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1084" t="inlineStr">
+      <c r="J1123" t="inlineStr">
         <is>
           <t>IRENA 2024</t>
         </is>
       </c>
     </row>
-    <row r="1085">
-      <c r="A1085" t="inlineStr">
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1085" t="n">
+      <c r="B1124" t="n">
         <v>0.042</v>
       </c>
-      <c r="C1085" t="inlineStr">
+      <c r="C1124" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="D1085" t="inlineStr">
+      <c r="D1124" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="E1085" t="inlineStr">
+      <c r="E1124" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F1085" t="inlineStr">
+      <c r="F1124" t="inlineStr">
         <is>
           <t>wacc</t>
         </is>
       </c>
-      <c r="G1085" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
-      <c r="H1085" t="inlineStr">
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1085" t="inlineStr">
+      <c r="I1124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1085" t="inlineStr">
+      <c r="J1124" t="inlineStr">
         <is>
           <t>IRENA 2024</t>
         </is>
       </c>
     </row>
-    <row r="1086">
-      <c r="A1086" t="inlineStr">
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1086" t="n">
+      <c r="B1125" t="n">
         <v>0.055</v>
       </c>
-      <c r="C1086" t="inlineStr">
+      <c r="C1125" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="D1086" t="inlineStr">
+      <c r="D1125" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="E1086" t="inlineStr">
+      <c r="E1125" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F1086" t="inlineStr">
+      <c r="F1125" t="inlineStr">
         <is>
           <t>wacc</t>
         </is>
       </c>
-      <c r="G1086" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
-      <c r="H1086" t="inlineStr">
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1086" t="inlineStr">
+      <c r="I1125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1086" t="inlineStr">
+      <c r="J1125" t="inlineStr">
         <is>
           <t>IRENA 2024</t>
         </is>
       </c>
     </row>
-    <row r="1087">
-      <c r="A1087" t="inlineStr">
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1087" t="n">
+      <c r="B1126" t="n">
         <v>0.077</v>
       </c>
-      <c r="C1087" t="inlineStr">
+      <c r="C1126" t="inlineStr">
         <is>
           <t>South America</t>
         </is>
       </c>
-      <c r="D1087" t="inlineStr">
+      <c r="D1126" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="E1087" t="inlineStr">
+      <c r="E1126" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F1087" t="inlineStr">
+      <c r="F1126" t="inlineStr">
         <is>
           <t>wacc</t>
         </is>
       </c>
-      <c r="G1087" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
-      <c r="H1087" t="inlineStr">
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1087" t="inlineStr">
+      <c r="I1126" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1087" t="inlineStr">
+      <c r="J1126" t="inlineStr">
         <is>
           <t>IRENA 2024</t>
         </is>
       </c>
     </row>
-    <row r="1088">
-      <c r="A1088" t="inlineStr">
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1088" t="n">
+      <c r="B1127" t="n">
         <v>0.039</v>
       </c>
-      <c r="C1088" t="inlineStr">
+      <c r="C1127" t="inlineStr">
         <is>
           <t>Oceania</t>
         </is>
       </c>
-      <c r="D1088" t="inlineStr">
+      <c r="D1127" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="E1088" t="inlineStr">
+      <c r="E1127" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F1088" t="inlineStr">
+      <c r="F1127" t="inlineStr">
         <is>
           <t>wacc</t>
         </is>
       </c>
-      <c r="G1088" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
-      <c r="H1088" t="inlineStr">
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1088" t="inlineStr">
+      <c r="I1127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1088" t="inlineStr">
+      <c r="J1127" t="inlineStr">
         <is>
           <t>IRENA 2024</t>
         </is>
       </c>
     </row>
-    <row r="1089">
-      <c r="A1089" t="inlineStr">
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1089" t="n">
+      <c r="B1128" t="n">
         <v>20</v>
       </c>
-      <c r="C1089" t="inlineStr">
+      <c r="C1128" t="inlineStr">
         <is>
           <t>World</t>
         </is>
       </c>
-      <c r="D1089" t="inlineStr">
+      <c r="D1128" t="inlineStr">
         <is>
           <t>Gas</t>
         </is>
       </c>
-      <c r="E1089" t="inlineStr">
+      <c r="E1128" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="F1089" t="inlineStr">
+      <c r="F1128" t="inlineStr">
         <is>
           <t>life</t>
         </is>
       </c>
-      <c r="G1089" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
-      <c r="H1089" t="inlineStr">
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1089" t="inlineStr">
+      <c r="I1128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1089" t="inlineStr">
+      <c r="J1128" t="inlineStr">
         <is>
           <t>Lazard 2025</t>
         </is>
       </c>
     </row>
-    <row r="1090">
-      <c r="A1090" t="inlineStr">
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1090" t="n">
+      <c r="B1129" t="n">
         <v>0.57</v>
       </c>
-      <c r="C1090" t="inlineStr">
+      <c r="C1129" t="inlineStr">
         <is>
           <t>World</t>
         </is>
       </c>
-      <c r="D1090" t="inlineStr">
+      <c r="D1129" t="inlineStr">
         <is>
           <t>Gas</t>
         </is>
       </c>
-      <c r="E1090" t="inlineStr">
+      <c r="E1129" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F1090" t="inlineStr">
+      <c r="F1129" t="inlineStr">
         <is>
           <t>efficiency</t>
         </is>
       </c>
-      <c r="G1090" t="inlineStr">
+      <c r="G1129" t="inlineStr">
         <is>
           <t>projected</t>
         </is>
       </c>
-      <c r="H1090" t="inlineStr">
+      <c r="H1129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1090" t="inlineStr">
+      <c r="I1129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1090" t="inlineStr">
+      <c r="J1129" t="inlineStr">
         <is>
           <t>GNESTE</t>
         </is>
       </c>
     </row>
-    <row r="1091">
-      <c r="A1091" t="inlineStr">
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1091" t="n">
+      <c r="B1130" t="n">
         <v>40</v>
       </c>
-      <c r="C1091" t="inlineStr">
+      <c r="C1130" t="inlineStr">
         <is>
           <t>World</t>
         </is>
       </c>
-      <c r="D1091" t="inlineStr">
+      <c r="D1130" t="inlineStr">
         <is>
           <t>Coal</t>
         </is>
       </c>
-      <c r="E1091" t="inlineStr">
+      <c r="E1130" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="F1091" t="inlineStr">
+      <c r="F1130" t="inlineStr">
         <is>
           <t>life</t>
         </is>
       </c>
-      <c r="G1091" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
-      <c r="H1091" t="inlineStr">
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1091" t="inlineStr">
+      <c r="I1130" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1091" t="inlineStr">
+      <c r="J1130" t="inlineStr">
         <is>
           <t>Lazard 2025</t>
         </is>
       </c>
     </row>
-    <row r="1092">
-      <c r="A1092" t="inlineStr">
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1092" t="n">
+      <c r="B1131" t="n">
         <v>0.43</v>
       </c>
-      <c r="C1092" t="inlineStr">
+      <c r="C1131" t="inlineStr">
         <is>
           <t>World</t>
         </is>
       </c>
-      <c r="D1092" t="inlineStr">
+      <c r="D1131" t="inlineStr">
         <is>
           <t>Coal</t>
         </is>
       </c>
-      <c r="E1092" t="inlineStr">
+      <c r="E1131" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F1092" t="inlineStr">
+      <c r="F1131" t="inlineStr">
         <is>
           <t>efficiency</t>
         </is>
       </c>
-      <c r="G1092" t="inlineStr">
+      <c r="G1131" t="inlineStr">
         <is>
           <t>projected</t>
         </is>
       </c>
-      <c r="H1092" t="inlineStr">
+      <c r="H1131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1092" t="inlineStr">
+      <c r="I1131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1092" t="inlineStr">
+      <c r="J1131" t="inlineStr">
         <is>
           <t>GNESTE</t>
         </is>
       </c>
     </row>
-    <row r="1093">
-      <c r="A1093" t="inlineStr">
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1093" t="n">
+      <c r="B1132" t="n">
         <v>20</v>
       </c>
-      <c r="C1093" t="inlineStr">
+      <c r="C1132" t="inlineStr">
         <is>
           <t>World</t>
         </is>
       </c>
-      <c r="D1093" t="inlineStr">
+      <c r="D1132" t="inlineStr">
         <is>
           <t>BESS</t>
         </is>
       </c>
-      <c r="E1093" t="inlineStr">
+      <c r="E1132" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="F1093" t="inlineStr">
+      <c r="F1132" t="inlineStr">
         <is>
           <t>life</t>
         </is>
       </c>
-      <c r="G1093" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
-      <c r="H1093" t="inlineStr">
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1093" t="inlineStr">
+      <c r="I1132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1093" t="inlineStr">
+      <c r="J1132" t="inlineStr">
         <is>
           <t>Lazard 2025</t>
         </is>
       </c>
     </row>
-    <row r="1094">
-      <c r="A1094" t="inlineStr">
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1094" t="n">
+      <c r="B1133" t="n">
         <v>35</v>
       </c>
-      <c r="C1094" t="inlineStr">
+      <c r="C1133" t="inlineStr">
         <is>
           <t>World</t>
         </is>
       </c>
-      <c r="D1094" t="inlineStr">
+      <c r="D1133" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="E1094" t="inlineStr">
+      <c r="E1133" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="F1094" t="inlineStr">
+      <c r="F1133" t="inlineStr">
         <is>
           <t>life</t>
         </is>
       </c>
-      <c r="G1094" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
-      <c r="H1094" t="inlineStr">
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1094" t="inlineStr">
+      <c r="I1133" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1094" t="inlineStr">
+      <c r="J1133" t="inlineStr">
         <is>
           <t>Lazard 2025</t>
         </is>
       </c>
     </row>
-    <row r="1095">
-      <c r="A1095" t="inlineStr">
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B1095" t="n">
+      <c r="B1134" t="n">
         <v>70</v>
       </c>
-      <c r="C1095" t="inlineStr">
+      <c r="C1134" t="inlineStr">
         <is>
           <t>World</t>
         </is>
       </c>
-      <c r="D1095" t="inlineStr">
+      <c r="D1134" t="inlineStr">
         <is>
           <t>Nuclear</t>
         </is>
       </c>
-      <c r="E1095" t="inlineStr">
+      <c r="E1134" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="F1095" t="inlineStr">
+      <c r="F1134" t="inlineStr">
         <is>
           <t>life</t>
         </is>
       </c>
-      <c r="G1095" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
-      <c r="H1095" t="inlineStr">
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I1095" t="inlineStr">
+      <c r="I1134" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J1095" t="inlineStr">
+      <c r="J1134" t="inlineStr">
         <is>
           <t>Lazard 2025</t>
         </is>

--- a/inputs/capex_opex_converted.xlsx
+++ b/inputs/capex_opex_converted.xlsx
@@ -15477,8 +15477,10 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="n">
-        <v>2023</v>
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="B328" t="n">
         <v>1412.62</v>
@@ -15523,15 +15525,17 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="n">
-        <v>2024</v>
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="B329" t="n">
-        <v>1412.62</v>
+        <v>1059.69</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15569,15 +15573,17 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="n">
-        <v>2025</v>
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="B330" t="n">
-        <v>1412.62</v>
+        <v>1023.18</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15615,15 +15621,17 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="n">
-        <v>2026</v>
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="B331" t="n">
-        <v>1412.62</v>
+        <v>1810.21</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15661,15 +15669,17 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="n">
-        <v>2027</v>
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="B332" t="n">
-        <v>1412.62</v>
+        <v>977.14</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -15707,15 +15717,17 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="n">
-        <v>2028</v>
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="B333" t="n">
-        <v>1412.62</v>
+        <v>1005.29</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15753,15 +15765,17 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="n">
-        <v>2029</v>
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="B334" t="n">
-        <v>1412.62</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -15799,15 +15813,17 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="n">
-        <v>2030</v>
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="B335" t="n">
-        <v>1412.62</v>
+        <v>750</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -15845,15 +15861,17 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="n">
-        <v>2031</v>
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="B336" t="n">
-        <v>1412.62</v>
+        <v>942.54</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -15891,15 +15909,17 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="n">
-        <v>2032</v>
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="B337" t="n">
-        <v>1412.62</v>
+        <v>1355.17</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -15938,7 +15958,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>2033</v>
+        <v>2024</v>
       </c>
       <c r="B338" t="n">
         <v>1412.62</v>
@@ -15984,14 +16004,14 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>2034</v>
+        <v>2024</v>
       </c>
       <c r="B339" t="n">
-        <v>1412.62</v>
+        <v>1059.69</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -16030,14 +16050,14 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>2035</v>
+        <v>2024</v>
       </c>
       <c r="B340" t="n">
-        <v>1412.62</v>
+        <v>1023.18</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -16076,14 +16096,14 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>2036</v>
+        <v>2024</v>
       </c>
       <c r="B341" t="n">
-        <v>1412.62</v>
+        <v>1810.21</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -16122,14 +16142,14 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>2037</v>
+        <v>2024</v>
       </c>
       <c r="B342" t="n">
-        <v>1412.62</v>
+        <v>977.14</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -16168,14 +16188,14 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>2038</v>
+        <v>2024</v>
       </c>
       <c r="B343" t="n">
-        <v>1412.62</v>
+        <v>1005.29</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -16214,14 +16234,14 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>2039</v>
+        <v>2024</v>
       </c>
       <c r="B344" t="n">
-        <v>1412.62</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -16260,14 +16280,14 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>2040</v>
+        <v>2024</v>
       </c>
       <c r="B345" t="n">
-        <v>1412.61</v>
+        <v>750</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -16306,14 +16326,14 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>2041</v>
+        <v>2024</v>
       </c>
       <c r="B346" t="n">
-        <v>1412.61</v>
+        <v>942.54</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -16352,14 +16372,14 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>2042</v>
+        <v>2024</v>
       </c>
       <c r="B347" t="n">
-        <v>1412.61</v>
+        <v>1355.17</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -16398,10 +16418,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>2043</v>
+        <v>2025</v>
       </c>
       <c r="B348" t="n">
-        <v>1412.61</v>
+        <v>1412.62</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -16444,14 +16464,14 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>2044</v>
+        <v>2025</v>
       </c>
       <c r="B349" t="n">
-        <v>1412.61</v>
+        <v>1059.69</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -16490,14 +16510,14 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>2045</v>
+        <v>2025</v>
       </c>
       <c r="B350" t="n">
-        <v>1412.61</v>
+        <v>1023.18</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -16536,14 +16556,14 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>2046</v>
+        <v>2025</v>
       </c>
       <c r="B351" t="n">
-        <v>1412.61</v>
+        <v>1810.21</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -16582,14 +16602,14 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>2047</v>
+        <v>2025</v>
       </c>
       <c r="B352" t="n">
-        <v>1412.61</v>
+        <v>977.14</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -16628,14 +16648,14 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>2048</v>
+        <v>2025</v>
       </c>
       <c r="B353" t="n">
-        <v>1412.61</v>
+        <v>1005.29</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -16674,14 +16694,14 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>2049</v>
+        <v>2025</v>
       </c>
       <c r="B354" t="n">
-        <v>1412.61</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -16720,14 +16740,14 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>2050</v>
+        <v>2025</v>
       </c>
       <c r="B355" t="n">
-        <v>1412.61</v>
+        <v>750</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -16766,14 +16786,14 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B356" t="n">
-        <v>1059.69</v>
+        <v>942.54</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -16812,14 +16832,14 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B357" t="n">
-        <v>1059.69</v>
+        <v>1355.17</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -16858,14 +16878,14 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B358" t="n">
-        <v>1059.69</v>
+        <v>1412.62</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -16950,14 +16970,14 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B360" t="n">
-        <v>1059.69</v>
+        <v>1023.18</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -16996,14 +17016,14 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="B361" t="n">
-        <v>1059.69</v>
+        <v>1810.21</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -17042,14 +17062,14 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="B362" t="n">
-        <v>1059.69</v>
+        <v>977.14</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -17088,14 +17108,14 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="B363" t="n">
-        <v>1059.69</v>
+        <v>1005.29</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -17134,14 +17154,14 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="B364" t="n">
-        <v>1059.69</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -17180,14 +17200,14 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>2032</v>
+        <v>2026</v>
       </c>
       <c r="B365" t="n">
-        <v>1059.69</v>
+        <v>750</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -17226,14 +17246,14 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>2033</v>
+        <v>2026</v>
       </c>
       <c r="B366" t="n">
-        <v>1059.69</v>
+        <v>942.54</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -17272,14 +17292,14 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>2034</v>
+        <v>2026</v>
       </c>
       <c r="B367" t="n">
-        <v>1059.69</v>
+        <v>1355.17</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -17318,14 +17338,14 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>2035</v>
+        <v>2027</v>
       </c>
       <c r="B368" t="n">
-        <v>1059.69</v>
+        <v>1412.62</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -17364,7 +17384,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>2036</v>
+        <v>2027</v>
       </c>
       <c r="B369" t="n">
         <v>1059.69</v>
@@ -17410,14 +17430,14 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>2037</v>
+        <v>2027</v>
       </c>
       <c r="B370" t="n">
-        <v>1059.69</v>
+        <v>1023.18</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -17456,14 +17476,14 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>2038</v>
+        <v>2027</v>
       </c>
       <c r="B371" t="n">
-        <v>1059.69</v>
+        <v>1810.21</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -17502,14 +17522,14 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>2039</v>
+        <v>2027</v>
       </c>
       <c r="B372" t="n">
-        <v>1059.69</v>
+        <v>977.14</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -17548,14 +17568,14 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>2040</v>
+        <v>2027</v>
       </c>
       <c r="B373" t="n">
-        <v>1059.69</v>
+        <v>1005.29</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -17594,14 +17614,14 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>2041</v>
+        <v>2027</v>
       </c>
       <c r="B374" t="n">
-        <v>1059.69</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -17640,14 +17660,14 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>2042</v>
+        <v>2027</v>
       </c>
       <c r="B375" t="n">
-        <v>1059.69</v>
+        <v>750</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -17686,14 +17706,14 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>2043</v>
+        <v>2027</v>
       </c>
       <c r="B376" t="n">
-        <v>1059.69</v>
+        <v>942.54</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -17732,14 +17752,14 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>2044</v>
+        <v>2027</v>
       </c>
       <c r="B377" t="n">
-        <v>1059.69</v>
+        <v>1355.17</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -17778,14 +17798,14 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>2045</v>
+        <v>2028</v>
       </c>
       <c r="B378" t="n">
-        <v>1059.69</v>
+        <v>1412.62</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -17824,7 +17844,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>2046</v>
+        <v>2028</v>
       </c>
       <c r="B379" t="n">
         <v>1059.69</v>
@@ -17870,14 +17890,14 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>2047</v>
+        <v>2028</v>
       </c>
       <c r="B380" t="n">
-        <v>1059.69</v>
+        <v>1023.18</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -17916,14 +17936,14 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>2048</v>
+        <v>2028</v>
       </c>
       <c r="B381" t="n">
-        <v>1059.69</v>
+        <v>1810.21</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -17962,14 +17982,14 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>2049</v>
+        <v>2028</v>
       </c>
       <c r="B382" t="n">
-        <v>1059.69</v>
+        <v>977.14</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -18008,14 +18028,14 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>2050</v>
+        <v>2028</v>
       </c>
       <c r="B383" t="n">
-        <v>1059.69</v>
+        <v>1005.29</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -18054,14 +18074,14 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="B384" t="n">
-        <v>1023.18</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -18100,14 +18120,14 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>2024</v>
+        <v>2028</v>
       </c>
       <c r="B385" t="n">
-        <v>1023.18</v>
+        <v>750</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -18146,14 +18166,14 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="B386" t="n">
-        <v>1023.18</v>
+        <v>942.54</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -18192,14 +18212,14 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="B387" t="n">
-        <v>1023.18</v>
+        <v>1355.17</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -18238,14 +18258,14 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="B388" t="n">
-        <v>1023.18</v>
+        <v>1412.62</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -18284,14 +18304,14 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B389" t="n">
-        <v>1023.18</v>
+        <v>1059.69</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -18376,14 +18396,14 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B391" t="n">
-        <v>1023.18</v>
+        <v>1810.21</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -18422,14 +18442,14 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="B392" t="n">
-        <v>1023.18</v>
+        <v>977.14</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -18468,14 +18488,14 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="B393" t="n">
-        <v>1023.18</v>
+        <v>1005.29</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -18514,14 +18534,14 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="B394" t="n">
-        <v>1023.18</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -18560,14 +18580,14 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="B395" t="n">
-        <v>1023.18</v>
+        <v>750</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -18606,14 +18626,14 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>2035</v>
+        <v>2029</v>
       </c>
       <c r="B396" t="n">
-        <v>1023.18</v>
+        <v>942.54</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -18652,14 +18672,14 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>2036</v>
+        <v>2029</v>
       </c>
       <c r="B397" t="n">
-        <v>1023.18</v>
+        <v>1355.17</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -18698,14 +18718,14 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>2037</v>
+        <v>2030</v>
       </c>
       <c r="B398" t="n">
-        <v>1023.18</v>
+        <v>1412.62</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -18744,14 +18764,14 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>2038</v>
+        <v>2030</v>
       </c>
       <c r="B399" t="n">
-        <v>1023.18</v>
+        <v>1059.69</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -18790,7 +18810,7 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>2039</v>
+        <v>2030</v>
       </c>
       <c r="B400" t="n">
         <v>1023.18</v>
@@ -18836,14 +18856,14 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B401" t="n">
-        <v>1023.18</v>
+        <v>1810.21</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -18882,14 +18902,14 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>2041</v>
+        <v>2030</v>
       </c>
       <c r="B402" t="n">
-        <v>1023.18</v>
+        <v>977.14</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -18928,14 +18948,14 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>2042</v>
+        <v>2030</v>
       </c>
       <c r="B403" t="n">
-        <v>1023.18</v>
+        <v>1005.29</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -18974,14 +18994,14 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>2043</v>
+        <v>2030</v>
       </c>
       <c r="B404" t="n">
-        <v>1023.18</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -19020,14 +19040,14 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>2044</v>
+        <v>2030</v>
       </c>
       <c r="B405" t="n">
-        <v>1023.18</v>
+        <v>750</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -19066,14 +19086,14 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>2045</v>
+        <v>2030</v>
       </c>
       <c r="B406" t="n">
-        <v>1023.18</v>
+        <v>942.54</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -19112,14 +19132,14 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>2046</v>
+        <v>2030</v>
       </c>
       <c r="B407" t="n">
-        <v>1023.18</v>
+        <v>1355.17</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -19158,14 +19178,14 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>2047</v>
+        <v>2031</v>
       </c>
       <c r="B408" t="n">
-        <v>1023.18</v>
+        <v>1412.62</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -19204,14 +19224,14 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>2048</v>
+        <v>2031</v>
       </c>
       <c r="B409" t="n">
-        <v>1023.18</v>
+        <v>1059.69</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -19250,7 +19270,7 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>2049</v>
+        <v>2031</v>
       </c>
       <c r="B410" t="n">
         <v>1023.18</v>
@@ -19296,14 +19316,14 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>2050</v>
+        <v>2031</v>
       </c>
       <c r="B411" t="n">
-        <v>1023.18</v>
+        <v>1810.21</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -19342,14 +19362,14 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>2023</v>
+        <v>2031</v>
       </c>
       <c r="B412" t="n">
-        <v>1810.21</v>
+        <v>977.14</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -19388,14 +19408,14 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>2024</v>
+        <v>2031</v>
       </c>
       <c r="B413" t="n">
-        <v>1810.21</v>
+        <v>1005.29</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -19434,14 +19454,14 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>2025</v>
+        <v>2031</v>
       </c>
       <c r="B414" t="n">
-        <v>1810.21</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -19480,14 +19500,14 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>2026</v>
+        <v>2031</v>
       </c>
       <c r="B415" t="n">
-        <v>1810.21</v>
+        <v>750</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -19526,14 +19546,14 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>2027</v>
+        <v>2031</v>
       </c>
       <c r="B416" t="n">
-        <v>1810.21</v>
+        <v>942.54</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -19572,14 +19592,14 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B417" t="n">
-        <v>1810.21</v>
+        <v>1355.17</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -19618,14 +19638,14 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="B418" t="n">
-        <v>1810.21</v>
+        <v>1412.62</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -19664,14 +19684,14 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="B419" t="n">
-        <v>1810.21</v>
+        <v>1059.69</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -19710,14 +19730,14 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B420" t="n">
-        <v>1810.21</v>
+        <v>1023.18</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -19802,14 +19822,14 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B422" t="n">
-        <v>1810.21</v>
+        <v>977.14</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -19848,14 +19868,14 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="B423" t="n">
-        <v>1810.21</v>
+        <v>1005.29</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -19894,14 +19914,14 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="B424" t="n">
-        <v>1810.21</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -19940,14 +19960,14 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="B425" t="n">
-        <v>1810.21</v>
+        <v>750</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -19986,14 +20006,14 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="B426" t="n">
-        <v>1810.21</v>
+        <v>942.54</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -20032,14 +20052,14 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>2038</v>
+        <v>2032</v>
       </c>
       <c r="B427" t="n">
-        <v>1810.21</v>
+        <v>1355.17</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -20078,14 +20098,14 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>2039</v>
+        <v>2033</v>
       </c>
       <c r="B428" t="n">
-        <v>1810.21</v>
+        <v>1412.62</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -20124,14 +20144,14 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>2040</v>
+        <v>2033</v>
       </c>
       <c r="B429" t="n">
-        <v>1810.21</v>
+        <v>1059.69</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -20170,14 +20190,14 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>2041</v>
+        <v>2033</v>
       </c>
       <c r="B430" t="n">
-        <v>1810.21</v>
+        <v>1023.18</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -20216,7 +20236,7 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>2042</v>
+        <v>2033</v>
       </c>
       <c r="B431" t="n">
         <v>1810.21</v>
@@ -20262,14 +20282,14 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>2043</v>
+        <v>2033</v>
       </c>
       <c r="B432" t="n">
-        <v>1810.21</v>
+        <v>977.14</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -20308,14 +20328,14 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>2044</v>
+        <v>2033</v>
       </c>
       <c r="B433" t="n">
-        <v>1810.21</v>
+        <v>1005.29</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -20354,14 +20374,14 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>2045</v>
+        <v>2033</v>
       </c>
       <c r="B434" t="n">
-        <v>1810.21</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -20400,14 +20420,14 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>2046</v>
+        <v>2033</v>
       </c>
       <c r="B435" t="n">
-        <v>1810.21</v>
+        <v>750</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -20446,14 +20466,14 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>2047</v>
+        <v>2033</v>
       </c>
       <c r="B436" t="n">
-        <v>1810.21</v>
+        <v>942.54</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -20492,14 +20512,14 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>2048</v>
+        <v>2033</v>
       </c>
       <c r="B437" t="n">
-        <v>1810.21</v>
+        <v>1355.17</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -20538,14 +20558,14 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>2049</v>
+        <v>2034</v>
       </c>
       <c r="B438" t="n">
-        <v>1810.21</v>
+        <v>1412.62</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -20584,14 +20604,14 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>2050</v>
+        <v>2034</v>
       </c>
       <c r="B439" t="n">
-        <v>1810.21</v>
+        <v>1059.69</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -20630,14 +20650,14 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>2023</v>
+        <v>2034</v>
       </c>
       <c r="B440" t="n">
-        <v>977.14</v>
+        <v>1023.18</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -20676,14 +20696,14 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="B441" t="n">
-        <v>977.14</v>
+        <v>1810.21</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -20722,7 +20742,7 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>2025</v>
+        <v>2034</v>
       </c>
       <c r="B442" t="n">
         <v>977.14</v>
@@ -20768,14 +20788,14 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>2026</v>
+        <v>2034</v>
       </c>
       <c r="B443" t="n">
-        <v>977.14</v>
+        <v>1005.29</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -20814,14 +20834,14 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>2027</v>
+        <v>2034</v>
       </c>
       <c r="B444" t="n">
-        <v>977.14</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -20860,14 +20880,14 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>2028</v>
+        <v>2034</v>
       </c>
       <c r="B445" t="n">
-        <v>977.14</v>
+        <v>750</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -20906,14 +20926,14 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="B446" t="n">
-        <v>977.14</v>
+        <v>942.54</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -20952,14 +20972,14 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="B447" t="n">
-        <v>977.14</v>
+        <v>1355.17</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -20998,14 +21018,14 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="B448" t="n">
-        <v>977.14</v>
+        <v>1412.62</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -21044,14 +21064,14 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="B449" t="n">
-        <v>977.14</v>
+        <v>1059.69</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -21090,14 +21110,14 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="B450" t="n">
-        <v>977.14</v>
+        <v>1023.18</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -21136,14 +21156,14 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B451" t="n">
-        <v>977.14</v>
+        <v>1810.21</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -21228,14 +21248,14 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B453" t="n">
-        <v>977.14</v>
+        <v>1005.29</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -21274,14 +21294,14 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="B454" t="n">
-        <v>977.14</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -21320,14 +21340,14 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="B455" t="n">
-        <v>977.14</v>
+        <v>750</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -21366,14 +21386,14 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>2039</v>
+        <v>2035</v>
       </c>
       <c r="B456" t="n">
-        <v>977.14</v>
+        <v>942.54</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -21412,14 +21432,14 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="B457" t="n">
-        <v>977.14</v>
+        <v>1355.17</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -21458,14 +21478,14 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="B458" t="n">
-        <v>977.14</v>
+        <v>1412.62</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -21504,14 +21524,14 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>2042</v>
+        <v>2036</v>
       </c>
       <c r="B459" t="n">
-        <v>977.14</v>
+        <v>1059.69</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -21550,14 +21570,14 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>2043</v>
+        <v>2036</v>
       </c>
       <c r="B460" t="n">
-        <v>977.14</v>
+        <v>1023.18</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -21596,14 +21616,14 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>2044</v>
+        <v>2036</v>
       </c>
       <c r="B461" t="n">
-        <v>977.14</v>
+        <v>1810.21</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -21642,7 +21662,7 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>2045</v>
+        <v>2036</v>
       </c>
       <c r="B462" t="n">
         <v>977.14</v>
@@ -21688,14 +21708,14 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>2046</v>
+        <v>2036</v>
       </c>
       <c r="B463" t="n">
-        <v>977.14</v>
+        <v>1005.29</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -21734,14 +21754,14 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>2047</v>
+        <v>2036</v>
       </c>
       <c r="B464" t="n">
-        <v>977.14</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -21780,14 +21800,14 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>2048</v>
+        <v>2036</v>
       </c>
       <c r="B465" t="n">
-        <v>977.14</v>
+        <v>750</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -21826,14 +21846,14 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>2049</v>
+        <v>2036</v>
       </c>
       <c r="B466" t="n">
-        <v>977.14</v>
+        <v>942.54</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -21872,14 +21892,14 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>2050</v>
+        <v>2036</v>
       </c>
       <c r="B467" t="n">
-        <v>977.14</v>
+        <v>1355.17</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -21918,14 +21938,14 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>2023</v>
+        <v>2037</v>
       </c>
       <c r="B468" t="n">
-        <v>1005.29</v>
+        <v>1412.62</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -21964,14 +21984,14 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>2024</v>
+        <v>2037</v>
       </c>
       <c r="B469" t="n">
-        <v>1005.29</v>
+        <v>1059.69</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -22010,14 +22030,14 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>2025</v>
+        <v>2037</v>
       </c>
       <c r="B470" t="n">
-        <v>1005.29</v>
+        <v>1023.18</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -22056,14 +22076,14 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>2026</v>
+        <v>2037</v>
       </c>
       <c r="B471" t="n">
-        <v>1005.29</v>
+        <v>1810.21</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -22102,14 +22122,14 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>2027</v>
+        <v>2037</v>
       </c>
       <c r="B472" t="n">
-        <v>1005.29</v>
+        <v>977.14</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -22148,7 +22168,7 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>2028</v>
+        <v>2037</v>
       </c>
       <c r="B473" t="n">
         <v>1005.29</v>
@@ -22194,14 +22214,14 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>2029</v>
+        <v>2037</v>
       </c>
       <c r="B474" t="n">
-        <v>1005.29</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -22240,14 +22260,14 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>2030</v>
+        <v>2037</v>
       </c>
       <c r="B475" t="n">
-        <v>1005.29</v>
+        <v>750</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -22286,14 +22306,14 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>2031</v>
+        <v>2037</v>
       </c>
       <c r="B476" t="n">
-        <v>1005.29</v>
+        <v>942.54</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -22332,14 +22352,14 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>2032</v>
+        <v>2037</v>
       </c>
       <c r="B477" t="n">
-        <v>1005.29</v>
+        <v>1355.17</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -22378,14 +22398,14 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>2033</v>
+        <v>2038</v>
       </c>
       <c r="B478" t="n">
-        <v>1005.29</v>
+        <v>1412.62</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -22424,14 +22444,14 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>2034</v>
+        <v>2038</v>
       </c>
       <c r="B479" t="n">
-        <v>1005.29</v>
+        <v>1059.69</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -22470,14 +22490,14 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="B480" t="n">
-        <v>1005.29</v>
+        <v>1023.18</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -22516,14 +22536,14 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="B481" t="n">
-        <v>1005.29</v>
+        <v>1810.21</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -22562,14 +22582,14 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B482" t="n">
-        <v>1005.29</v>
+        <v>977.14</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -22654,14 +22674,14 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B484" t="n">
-        <v>1005.29</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -22700,14 +22720,14 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="B485" t="n">
-        <v>1005.29</v>
+        <v>750</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -22746,14 +22766,14 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>2041</v>
+        <v>2038</v>
       </c>
       <c r="B486" t="n">
-        <v>1005.29</v>
+        <v>942.54</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -22792,14 +22812,14 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>2042</v>
+        <v>2038</v>
       </c>
       <c r="B487" t="n">
-        <v>1005.29</v>
+        <v>1355.17</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -22838,14 +22858,14 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="B488" t="n">
-        <v>1005.29</v>
+        <v>1412.62</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -22884,14 +22904,14 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="B489" t="n">
-        <v>1005.29</v>
+        <v>1059.69</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -22930,14 +22950,14 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>2045</v>
+        <v>2039</v>
       </c>
       <c r="B490" t="n">
-        <v>1005.29</v>
+        <v>1023.18</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -22976,14 +22996,14 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>2046</v>
+        <v>2039</v>
       </c>
       <c r="B491" t="n">
-        <v>1005.29</v>
+        <v>1810.21</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -23022,14 +23042,14 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>2047</v>
+        <v>2039</v>
       </c>
       <c r="B492" t="n">
-        <v>1005.29</v>
+        <v>977.14</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -23068,7 +23088,7 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>2048</v>
+        <v>2039</v>
       </c>
       <c r="B493" t="n">
         <v>1005.29</v>
@@ -23114,14 +23134,14 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>2049</v>
+        <v>2039</v>
       </c>
       <c r="B494" t="n">
-        <v>1005.29</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -23160,14 +23180,14 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>2050</v>
+        <v>2039</v>
       </c>
       <c r="B495" t="n">
-        <v>1005.29</v>
+        <v>750</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Non-EU Europe</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -23206,14 +23226,14 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>2023</v>
+        <v>2039</v>
       </c>
       <c r="B496" t="n">
-        <v>635.4299999999999</v>
+        <v>942.54</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -23252,14 +23272,14 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>2024</v>
+        <v>2039</v>
       </c>
       <c r="B497" t="n">
-        <v>635.4299999999999</v>
+        <v>1355.17</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -23298,14 +23318,14 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>2025</v>
+        <v>2040</v>
       </c>
       <c r="B498" t="n">
-        <v>635.4299999999999</v>
+        <v>1412.61</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -23344,14 +23364,14 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>2026</v>
+        <v>2040</v>
       </c>
       <c r="B499" t="n">
-        <v>635.4299999999999</v>
+        <v>1059.69</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -23390,14 +23410,14 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>2027</v>
+        <v>2040</v>
       </c>
       <c r="B500" t="n">
-        <v>635.4299999999999</v>
+        <v>1023.18</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -23436,14 +23456,14 @@
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>2028</v>
+        <v>2040</v>
       </c>
       <c r="B501" t="n">
-        <v>635.4299999999999</v>
+        <v>1810.21</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -23482,14 +23502,14 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>2029</v>
+        <v>2040</v>
       </c>
       <c r="B502" t="n">
-        <v>635.4299999999999</v>
+        <v>977.14</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -23528,14 +23548,14 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="B503" t="n">
-        <v>635.4299999999999</v>
+        <v>1005.29</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -23574,7 +23594,7 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>2031</v>
+        <v>2040</v>
       </c>
       <c r="B504" t="n">
         <v>635.4299999999999</v>
@@ -23620,14 +23640,14 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>2032</v>
+        <v>2040</v>
       </c>
       <c r="B505" t="n">
-        <v>635.4299999999999</v>
+        <v>750</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -23666,14 +23686,14 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>2033</v>
+        <v>2040</v>
       </c>
       <c r="B506" t="n">
-        <v>635.4299999999999</v>
+        <v>942.54</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -23712,14 +23732,14 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>2034</v>
+        <v>2040</v>
       </c>
       <c r="B507" t="n">
-        <v>635.4299999999999</v>
+        <v>1355.17</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -23758,14 +23778,14 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>2035</v>
+        <v>2041</v>
       </c>
       <c r="B508" t="n">
-        <v>635.4299999999999</v>
+        <v>1412.61</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -23804,14 +23824,14 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>2036</v>
+        <v>2041</v>
       </c>
       <c r="B509" t="n">
-        <v>635.4299999999999</v>
+        <v>1059.69</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -23850,14 +23870,14 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>2037</v>
+        <v>2041</v>
       </c>
       <c r="B510" t="n">
-        <v>635.4299999999999</v>
+        <v>1023.18</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -23896,14 +23916,14 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="B511" t="n">
-        <v>635.4299999999999</v>
+        <v>1810.21</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -23942,14 +23962,14 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="B512" t="n">
-        <v>635.4299999999999</v>
+        <v>977.14</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -23988,14 +24008,14 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="B513" t="n">
-        <v>635.4299999999999</v>
+        <v>1005.29</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -24080,14 +24100,14 @@
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B515" t="n">
-        <v>635.4299999999999</v>
+        <v>750</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -24126,14 +24146,14 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="B516" t="n">
-        <v>635.4299999999999</v>
+        <v>942.54</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -24172,14 +24192,14 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>2044</v>
+        <v>2041</v>
       </c>
       <c r="B517" t="n">
-        <v>635.4299999999999</v>
+        <v>1355.17</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -24218,14 +24238,14 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>2045</v>
+        <v>2042</v>
       </c>
       <c r="B518" t="n">
-        <v>635.4299999999999</v>
+        <v>1412.61</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -24264,14 +24284,14 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="B519" t="n">
-        <v>635.4299999999999</v>
+        <v>1059.69</v>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -24310,14 +24330,14 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="B520" t="n">
-        <v>635.4299999999999</v>
+        <v>1023.18</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -24356,14 +24376,14 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>2048</v>
+        <v>2042</v>
       </c>
       <c r="B521" t="n">
-        <v>635.4299999999999</v>
+        <v>1810.21</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -24402,14 +24422,14 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>2049</v>
+        <v>2042</v>
       </c>
       <c r="B522" t="n">
-        <v>635.4299999999999</v>
+        <v>977.14</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -24448,14 +24468,14 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>2050</v>
+        <v>2042</v>
       </c>
       <c r="B523" t="n">
-        <v>635.4299999999999</v>
+        <v>1005.29</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -24494,14 +24514,14 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>2023</v>
+        <v>2042</v>
       </c>
       <c r="B524" t="n">
-        <v>750</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -24540,7 +24560,7 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>2024</v>
+        <v>2042</v>
       </c>
       <c r="B525" t="n">
         <v>750</v>
@@ -24586,14 +24606,14 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>2025</v>
+        <v>2042</v>
       </c>
       <c r="B526" t="n">
-        <v>750</v>
+        <v>942.54</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -24632,14 +24652,14 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>2026</v>
+        <v>2042</v>
       </c>
       <c r="B527" t="n">
-        <v>750</v>
+        <v>1355.17</v>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -24678,14 +24698,14 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>2027</v>
+        <v>2043</v>
       </c>
       <c r="B528" t="n">
-        <v>750</v>
+        <v>1412.61</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -24724,14 +24744,14 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>2028</v>
+        <v>2043</v>
       </c>
       <c r="B529" t="n">
-        <v>750</v>
+        <v>1059.69</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -24770,14 +24790,14 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>2029</v>
+        <v>2043</v>
       </c>
       <c r="B530" t="n">
-        <v>750</v>
+        <v>1023.18</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -24816,14 +24836,14 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>2030</v>
+        <v>2043</v>
       </c>
       <c r="B531" t="n">
-        <v>750</v>
+        <v>1810.21</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -24862,14 +24882,14 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>2031</v>
+        <v>2043</v>
       </c>
       <c r="B532" t="n">
-        <v>750</v>
+        <v>977.14</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -24908,14 +24928,14 @@
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>2032</v>
+        <v>2043</v>
       </c>
       <c r="B533" t="n">
-        <v>750</v>
+        <v>1005.29</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -24954,14 +24974,14 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>2033</v>
+        <v>2043</v>
       </c>
       <c r="B534" t="n">
-        <v>750</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -25000,7 +25020,7 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>2034</v>
+        <v>2043</v>
       </c>
       <c r="B535" t="n">
         <v>750</v>
@@ -25046,14 +25066,14 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>2035</v>
+        <v>2043</v>
       </c>
       <c r="B536" t="n">
-        <v>750</v>
+        <v>942.54</v>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -25092,14 +25112,14 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>2036</v>
+        <v>2043</v>
       </c>
       <c r="B537" t="n">
-        <v>750</v>
+        <v>1355.17</v>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -25138,14 +25158,14 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>2037</v>
+        <v>2044</v>
       </c>
       <c r="B538" t="n">
-        <v>750</v>
+        <v>1412.61</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -25184,14 +25204,14 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>2038</v>
+        <v>2044</v>
       </c>
       <c r="B539" t="n">
-        <v>750</v>
+        <v>1059.69</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -25230,14 +25250,14 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>2039</v>
+        <v>2044</v>
       </c>
       <c r="B540" t="n">
-        <v>750</v>
+        <v>1023.18</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -25276,14 +25296,14 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>2040</v>
+        <v>2044</v>
       </c>
       <c r="B541" t="n">
-        <v>750</v>
+        <v>1810.21</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -25322,14 +25342,14 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="B542" t="n">
-        <v>750</v>
+        <v>977.14</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -25368,14 +25388,14 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="B543" t="n">
-        <v>750</v>
+        <v>1005.29</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -25414,14 +25434,14 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="B544" t="n">
-        <v>750</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -25506,14 +25526,14 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B546" t="n">
-        <v>750</v>
+        <v>942.54</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -25552,14 +25572,14 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="B547" t="n">
-        <v>750</v>
+        <v>1355.17</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -25598,14 +25618,14 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="B548" t="n">
-        <v>750</v>
+        <v>1412.61</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -25644,14 +25664,14 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>2048</v>
+        <v>2045</v>
       </c>
       <c r="B549" t="n">
-        <v>750</v>
+        <v>1059.69</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -25690,14 +25710,14 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>2049</v>
+        <v>2045</v>
       </c>
       <c r="B550" t="n">
-        <v>750</v>
+        <v>1023.18</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -25736,14 +25756,14 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="B551" t="n">
-        <v>750</v>
+        <v>1810.21</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -25782,14 +25802,14 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>2023</v>
+        <v>2045</v>
       </c>
       <c r="B552" t="n">
-        <v>942.54</v>
+        <v>977.14</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -25828,14 +25848,14 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>2024</v>
+        <v>2045</v>
       </c>
       <c r="B553" t="n">
-        <v>942.54</v>
+        <v>1005.29</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -25874,14 +25894,14 @@
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>2025</v>
+        <v>2045</v>
       </c>
       <c r="B554" t="n">
-        <v>942.54</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -25920,14 +25940,14 @@
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>2026</v>
+        <v>2045</v>
       </c>
       <c r="B555" t="n">
-        <v>942.54</v>
+        <v>750</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -25966,7 +25986,7 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>2027</v>
+        <v>2045</v>
       </c>
       <c r="B556" t="n">
         <v>942.54</v>
@@ -26012,14 +26032,14 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>2028</v>
+        <v>2045</v>
       </c>
       <c r="B557" t="n">
-        <v>942.54</v>
+        <v>1355.17</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -26058,14 +26078,14 @@
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>2029</v>
+        <v>2046</v>
       </c>
       <c r="B558" t="n">
-        <v>942.54</v>
+        <v>1412.61</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -26104,14 +26124,14 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>2030</v>
+        <v>2046</v>
       </c>
       <c r="B559" t="n">
-        <v>942.54</v>
+        <v>1059.69</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -26150,14 +26170,14 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>2031</v>
+        <v>2046</v>
       </c>
       <c r="B560" t="n">
-        <v>942.54</v>
+        <v>1023.18</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -26196,14 +26216,14 @@
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>2032</v>
+        <v>2046</v>
       </c>
       <c r="B561" t="n">
-        <v>942.54</v>
+        <v>1810.21</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -26242,14 +26262,14 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>2033</v>
+        <v>2046</v>
       </c>
       <c r="B562" t="n">
-        <v>942.54</v>
+        <v>977.14</v>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -26288,14 +26308,14 @@
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>2034</v>
+        <v>2046</v>
       </c>
       <c r="B563" t="n">
-        <v>942.54</v>
+        <v>1005.29</v>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -26334,14 +26354,14 @@
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>2035</v>
+        <v>2046</v>
       </c>
       <c r="B564" t="n">
-        <v>942.54</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -26380,14 +26400,14 @@
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>2036</v>
+        <v>2046</v>
       </c>
       <c r="B565" t="n">
-        <v>942.54</v>
+        <v>750</v>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -26426,7 +26446,7 @@
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>2037</v>
+        <v>2046</v>
       </c>
       <c r="B566" t="n">
         <v>942.54</v>
@@ -26472,14 +26492,14 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>2038</v>
+        <v>2046</v>
       </c>
       <c r="B567" t="n">
-        <v>942.54</v>
+        <v>1355.17</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -26518,14 +26538,14 @@
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>2039</v>
+        <v>2047</v>
       </c>
       <c r="B568" t="n">
-        <v>942.54</v>
+        <v>1412.61</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -26564,14 +26584,14 @@
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>2040</v>
+        <v>2047</v>
       </c>
       <c r="B569" t="n">
-        <v>942.54</v>
+        <v>1059.69</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -26610,14 +26630,14 @@
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>2041</v>
+        <v>2047</v>
       </c>
       <c r="B570" t="n">
-        <v>942.54</v>
+        <v>1023.18</v>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -26656,14 +26676,14 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>2042</v>
+        <v>2047</v>
       </c>
       <c r="B571" t="n">
-        <v>942.54</v>
+        <v>1810.21</v>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -26702,14 +26722,14 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>2043</v>
+        <v>2047</v>
       </c>
       <c r="B572" t="n">
-        <v>942.54</v>
+        <v>977.14</v>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -26748,14 +26768,14 @@
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="B573" t="n">
-        <v>942.54</v>
+        <v>1005.29</v>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -26794,14 +26814,14 @@
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="B574" t="n">
-        <v>942.54</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -26840,14 +26860,14 @@
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B575" t="n">
-        <v>942.54</v>
+        <v>750</v>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -26932,14 +26952,14 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B577" t="n">
-        <v>942.54</v>
+        <v>1355.17</v>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Other Pacific Asia</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -26978,14 +26998,14 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B578" t="n">
-        <v>942.54</v>
+        <v>1412.61</v>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -27024,14 +27044,14 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="B579" t="n">
-        <v>942.54</v>
+        <v>1059.69</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>South East Asia</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -27070,14 +27090,14 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>2023</v>
+        <v>2048</v>
       </c>
       <c r="B580" t="n">
-        <v>1355.17</v>
+        <v>1023.18</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -27116,14 +27136,14 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>2024</v>
+        <v>2048</v>
       </c>
       <c r="B581" t="n">
-        <v>1355.17</v>
+        <v>1810.21</v>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -27162,14 +27182,14 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>2025</v>
+        <v>2048</v>
       </c>
       <c r="B582" t="n">
-        <v>1355.17</v>
+        <v>977.14</v>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -27208,14 +27228,14 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="B583" t="n">
-        <v>1355.17</v>
+        <v>1005.29</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -27254,14 +27274,14 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>2027</v>
+        <v>2048</v>
       </c>
       <c r="B584" t="n">
-        <v>1355.17</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -27300,14 +27320,14 @@
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>2028</v>
+        <v>2048</v>
       </c>
       <c r="B585" t="n">
-        <v>1355.17</v>
+        <v>750</v>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -27346,14 +27366,14 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>2029</v>
+        <v>2048</v>
       </c>
       <c r="B586" t="n">
-        <v>1355.17</v>
+        <v>942.54</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -27392,7 +27412,7 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>2030</v>
+        <v>2048</v>
       </c>
       <c r="B587" t="n">
         <v>1355.17</v>
@@ -27438,14 +27458,14 @@
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>2031</v>
+        <v>2049</v>
       </c>
       <c r="B588" t="n">
-        <v>1355.17</v>
+        <v>1412.61</v>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -27484,14 +27504,14 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>2032</v>
+        <v>2049</v>
       </c>
       <c r="B589" t="n">
-        <v>1355.17</v>
+        <v>1059.69</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -27530,14 +27550,14 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>2033</v>
+        <v>2049</v>
       </c>
       <c r="B590" t="n">
-        <v>1355.17</v>
+        <v>1023.18</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -27576,14 +27596,14 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>2034</v>
+        <v>2049</v>
       </c>
       <c r="B591" t="n">
-        <v>1355.17</v>
+        <v>1810.21</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -27622,14 +27642,14 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>2035</v>
+        <v>2049</v>
       </c>
       <c r="B592" t="n">
-        <v>1355.17</v>
+        <v>977.14</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -27668,14 +27688,14 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>2036</v>
+        <v>2049</v>
       </c>
       <c r="B593" t="n">
-        <v>1355.17</v>
+        <v>1005.29</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -27714,14 +27734,14 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>2037</v>
+        <v>2049</v>
       </c>
       <c r="B594" t="n">
-        <v>1355.17</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -27760,14 +27780,14 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>2038</v>
+        <v>2049</v>
       </c>
       <c r="B595" t="n">
-        <v>1355.17</v>
+        <v>750</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -27806,14 +27826,14 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>2039</v>
+        <v>2049</v>
       </c>
       <c r="B596" t="n">
-        <v>1355.17</v>
+        <v>942.54</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -27852,7 +27872,7 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>2040</v>
+        <v>2049</v>
       </c>
       <c r="B597" t="n">
         <v>1355.17</v>
@@ -27898,14 +27918,14 @@
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>2041</v>
+        <v>2050</v>
       </c>
       <c r="B598" t="n">
-        <v>1355.17</v>
+        <v>1412.61</v>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -27944,14 +27964,14 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>2042</v>
+        <v>2050</v>
       </c>
       <c r="B599" t="n">
-        <v>1355.17</v>
+        <v>1059.69</v>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -27990,14 +28010,14 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>2043</v>
+        <v>2050</v>
       </c>
       <c r="B600" t="n">
-        <v>1355.17</v>
+        <v>1023.18</v>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -28036,14 +28056,14 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>2044</v>
+        <v>2050</v>
       </c>
       <c r="B601" t="n">
-        <v>1355.17</v>
+        <v>1810.21</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Sub-Saharan Africa</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -28082,14 +28102,14 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="B602" t="n">
-        <v>1355.17</v>
+        <v>977.14</v>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -28128,14 +28148,14 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>2046</v>
+        <v>2050</v>
       </c>
       <c r="B603" t="n">
-        <v>1355.17</v>
+        <v>1005.29</v>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>Non-EU Europe</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -28174,14 +28194,14 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>2047</v>
+        <v>2050</v>
       </c>
       <c r="B604" t="n">
-        <v>1355.17</v>
+        <v>635.4299999999999</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -28220,14 +28240,14 @@
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="B605" t="n">
-        <v>1355.17</v>
+        <v>750</v>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -28266,14 +28286,14 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B606" t="n">
-        <v>1355.17</v>
+        <v>942.54</v>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Other Pacific Asia</t>
+          <t>South East Asia</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">

--- a/inputs/capex_opex_converted.xlsx
+++ b/inputs/capex_opex_converted.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1277"/>
+  <dimension ref="A1:K1278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51564,7 +51564,7 @@
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>5.25</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="C1088" t="inlineStr">
         <is>
@@ -51578,12 +51578,12 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t>kWh/year</t>
+          <t>MWh</t>
         </is>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
-          <t>opex_f</t>
+          <t>opex_v</t>
         </is>
       </c>
       <c r="G1088" t="inlineStr"/>
@@ -51602,7 +51602,7 @@
       </c>
       <c r="K1088" t="inlineStr">
         <is>
-          <t>Lazard 2024</t>
+          <t>Schmidt 2023</t>
         </is>
       </c>
     </row>
@@ -53444,7 +53444,7 @@
         <v>2025</v>
       </c>
       <c r="B1128" t="n">
-        <v>1.196735571358385</v>
+        <v>15.50969176402933</v>
       </c>
       <c r="C1128" t="inlineStr">
         <is>
@@ -53487,7 +53487,7 @@
         <v>2026</v>
       </c>
       <c r="B1129" t="n">
-        <v>1.285826199208117</v>
+        <v>16.66430620859269</v>
       </c>
       <c r="C1129" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>2027</v>
       </c>
       <c r="B1130" t="n">
-        <v>1.349791109662167</v>
+        <v>17.49329138175838</v>
       </c>
       <c r="C1130" t="inlineStr">
         <is>
@@ -53573,7 +53573,7 @@
         <v>2028</v>
       </c>
       <c r="B1131" t="n">
-        <v>1.352468055253857</v>
+        <v>17.52798459385122</v>
       </c>
       <c r="C1131" t="inlineStr">
         <is>
@@ -53616,7 +53616,7 @@
         <v>2029</v>
       </c>
       <c r="B1132" t="n">
-        <v>1.349180578211431</v>
+        <v>17.48537889478984</v>
       </c>
       <c r="C1132" t="inlineStr">
         <is>
@@ -53659,7 +53659,7 @@
         <v>2030</v>
       </c>
       <c r="B1133" t="n">
-        <v>1.350730388817146</v>
+        <v>17.50546443863306</v>
       </c>
       <c r="C1133" t="inlineStr">
         <is>
@@ -53698,11 +53698,13 @@
       <c r="K1133" t="inlineStr"/>
     </row>
     <row r="1134">
-      <c r="A1134" t="n">
-        <v>2010</v>
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
       <c r="B1134" t="n">
-        <v>1285.7</v>
+        <v>5.4</v>
       </c>
       <c r="C1134" t="inlineStr">
         <is>
@@ -53716,12 +53718,12 @@
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>kWh</t>
+          <t>kW</t>
         </is>
       </c>
       <c r="F1134" t="inlineStr">
         <is>
-          <t>capex_e</t>
+          <t>opex_f</t>
         </is>
       </c>
       <c r="G1134" t="inlineStr"/>
@@ -53740,16 +53742,16 @@
       </c>
       <c r="K1134" t="inlineStr">
         <is>
-          <t>IRENA 2024</t>
+          <t>Schmidt 2023</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B1135" t="n">
-        <v>1065.8</v>
+        <v>1285.7</v>
       </c>
       <c r="C1135" t="inlineStr">
         <is>
@@ -53793,10 +53795,10 @@
     </row>
     <row r="1136">
       <c r="A1136" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B1136" t="n">
-        <v>1005.1</v>
+        <v>1065.8</v>
       </c>
       <c r="C1136" t="inlineStr">
         <is>
@@ -53840,10 +53842,10 @@
     </row>
     <row r="1137">
       <c r="A1137" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B1137" t="n">
-        <v>827.5</v>
+        <v>1005.1</v>
       </c>
       <c r="C1137" t="inlineStr">
         <is>
@@ -53887,10 +53889,10 @@
     </row>
     <row r="1138">
       <c r="A1138" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B1138" t="n">
-        <v>870.8</v>
+        <v>827.5</v>
       </c>
       <c r="C1138" t="inlineStr">
         <is>
@@ -53934,10 +53936,10 @@
     </row>
     <row r="1139">
       <c r="A1139" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B1139" t="n">
-        <v>772</v>
+        <v>870.8</v>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
@@ -53981,10 +53983,10 @@
     </row>
     <row r="1140">
       <c r="A1140" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B1140" t="n">
-        <v>551</v>
+        <v>772</v>
       </c>
       <c r="C1140" t="inlineStr">
         <is>
@@ -54028,10 +54030,10 @@
     </row>
     <row r="1141">
       <c r="A1141" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B1141" t="n">
-        <v>394.85</v>
+        <v>551</v>
       </c>
       <c r="C1141" t="inlineStr">
         <is>
@@ -54075,10 +54077,10 @@
     </row>
     <row r="1142">
       <c r="A1142" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B1142" t="n">
-        <v>355.35</v>
+        <v>394.85</v>
       </c>
       <c r="C1142" t="inlineStr">
         <is>
@@ -54122,10 +54124,10 @@
     </row>
     <row r="1143">
       <c r="A1143" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B1143" t="n">
-        <v>166.55</v>
+        <v>355.35</v>
       </c>
       <c r="C1143" t="inlineStr">
         <is>
@@ -54169,10 +54171,10 @@
     </row>
     <row r="1144">
       <c r="A1144" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B1144" t="n">
-        <v>149.95</v>
+        <v>166.55</v>
       </c>
       <c r="C1144" t="inlineStr">
         <is>
@@ -54216,10 +54218,10 @@
     </row>
     <row r="1145">
       <c r="A1145" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B1145" t="n">
-        <v>140.9</v>
+        <v>149.95</v>
       </c>
       <c r="C1145" t="inlineStr">
         <is>
@@ -54263,10 +54265,10 @@
     </row>
     <row r="1146">
       <c r="A1146" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B1146" t="n">
-        <v>178.5</v>
+        <v>140.9</v>
       </c>
       <c r="C1146" t="inlineStr">
         <is>
@@ -54310,10 +54312,10 @@
     </row>
     <row r="1147">
       <c r="A1147" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B1147" t="n">
-        <v>135.9</v>
+        <v>178.5</v>
       </c>
       <c r="C1147" t="inlineStr">
         <is>
@@ -54357,10 +54359,10 @@
     </row>
     <row r="1148">
       <c r="A1148" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B1148" t="n">
-        <v>95.8</v>
+        <v>135.9</v>
       </c>
       <c r="C1148" t="inlineStr">
         <is>
@@ -54404,10 +54406,10 @@
     </row>
     <row r="1149">
       <c r="A1149" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B1149" t="n">
-        <v>94.83232323232323</v>
+        <v>95.8</v>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
@@ -54432,7 +54434,7 @@
       <c r="G1149" t="inlineStr"/>
       <c r="H1149" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>historic</t>
         </is>
       </c>
       <c r="I1149" t="inlineStr">
@@ -54443,14 +54445,18 @@
       <c r="J1149" t="n">
         <v>2025</v>
       </c>
-      <c r="K1149" t="inlineStr"/>
+      <c r="K1149" t="inlineStr">
+        <is>
+          <t>IRENA 2024</t>
+        </is>
+      </c>
     </row>
     <row r="1150">
       <c r="A1150" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B1150" t="n">
-        <v>93.90000000000001</v>
+        <v>94.83232323232323</v>
       </c>
       <c r="C1150" t="inlineStr">
         <is>
@@ -54490,10 +54496,10 @@
     </row>
     <row r="1151">
       <c r="A1151" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B1151" t="n">
-        <v>92.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="C1151" t="inlineStr">
         <is>
@@ -54533,10 +54539,10 @@
     </row>
     <row r="1152">
       <c r="A1152" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1152" t="n">
-        <v>92</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
@@ -54576,10 +54582,10 @@
     </row>
     <row r="1153">
       <c r="A1153" t="n">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B1153" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C1153" t="inlineStr">
         <is>
@@ -54619,10 +54625,10 @@
     </row>
     <row r="1154">
       <c r="A1154" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B1154" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1154" t="inlineStr">
         <is>
@@ -54662,10 +54668,10 @@
     </row>
     <row r="1155">
       <c r="A1155" t="n">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B1155" t="n">
-        <v>89.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
@@ -54705,10 +54711,10 @@
     </row>
     <row r="1156">
       <c r="A1156" t="n">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B1156" t="n">
-        <v>88.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C1156" t="inlineStr">
         <is>
@@ -54748,10 +54754,10 @@
     </row>
     <row r="1157">
       <c r="A1157" t="n">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B1157" t="n">
-        <v>87.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C1157" t="inlineStr">
         <is>
@@ -54791,10 +54797,10 @@
     </row>
     <row r="1158">
       <c r="A1158" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B1158" t="n">
-        <v>86.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="C1158" t="inlineStr">
         <is>
@@ -54834,10 +54840,10 @@
     </row>
     <row r="1159">
       <c r="A1159" t="n">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B1159" t="n">
-        <v>85.7</v>
+        <v>86.7</v>
       </c>
       <c r="C1159" t="inlineStr">
         <is>
@@ -54877,10 +54883,10 @@
     </row>
     <row r="1160">
       <c r="A1160" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B1160" t="n">
-        <v>84.8</v>
+        <v>85.7</v>
       </c>
       <c r="C1160" t="inlineStr">
         <is>
@@ -54920,10 +54926,10 @@
     </row>
     <row r="1161">
       <c r="A1161" t="n">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B1161" t="n">
-        <v>83.8</v>
+        <v>84.8</v>
       </c>
       <c r="C1161" t="inlineStr">
         <is>
@@ -54963,10 +54969,10 @@
     </row>
     <row r="1162">
       <c r="A1162" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B1162" t="n">
-        <v>83.3</v>
+        <v>83.8</v>
       </c>
       <c r="C1162" t="inlineStr">
         <is>
@@ -55006,10 +55012,10 @@
     </row>
     <row r="1163">
       <c r="A1163" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B1163" t="n">
-        <v>82.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="C1163" t="inlineStr">
         <is>
@@ -55049,10 +55055,10 @@
     </row>
     <row r="1164">
       <c r="A1164" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B1164" t="n">
-        <v>81.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C1164" t="inlineStr">
         <is>
@@ -55092,10 +55098,10 @@
     </row>
     <row r="1165">
       <c r="A1165" t="n">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B1165" t="n">
-        <v>80.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C1165" t="inlineStr">
         <is>
@@ -55135,10 +55141,10 @@
     </row>
     <row r="1166">
       <c r="A1166" t="n">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B1166" t="n">
-        <v>80</v>
+        <v>80.5</v>
       </c>
       <c r="C1166" t="inlineStr">
         <is>
@@ -55178,10 +55184,10 @@
     </row>
     <row r="1167">
       <c r="A1167" t="n">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B1167" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
@@ -55221,10 +55227,10 @@
     </row>
     <row r="1168">
       <c r="A1168" t="n">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B1168" t="n">
-        <v>78.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="C1168" t="inlineStr">
         <is>
@@ -55264,10 +55270,10 @@
     </row>
     <row r="1169">
       <c r="A1169" t="n">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B1169" t="n">
-        <v>77.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="C1169" t="inlineStr">
         <is>
@@ -55307,10 +55313,10 @@
     </row>
     <row r="1170">
       <c r="A1170" t="n">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B1170" t="n">
-        <v>76.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="C1170" t="inlineStr">
         <is>
@@ -55350,10 +55356,10 @@
     </row>
     <row r="1171">
       <c r="A1171" t="n">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B1171" t="n">
-        <v>75.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="C1171" t="inlineStr">
         <is>
@@ -55393,10 +55399,10 @@
     </row>
     <row r="1172">
       <c r="A1172" t="n">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B1172" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="C1172" t="inlineStr">
         <is>
@@ -55436,10 +55442,10 @@
     </row>
     <row r="1173">
       <c r="A1173" t="n">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B1173" t="n">
-        <v>74.2</v>
+        <v>75.2</v>
       </c>
       <c r="C1173" t="inlineStr">
         <is>
@@ -55479,10 +55485,10 @@
     </row>
     <row r="1174">
       <c r="A1174" t="n">
-        <v>2010</v>
+        <v>2049</v>
       </c>
       <c r="B1174" t="n">
-        <v>5142.8</v>
+        <v>74.2</v>
       </c>
       <c r="C1174" t="inlineStr">
         <is>
@@ -55496,18 +55502,18 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>kW</t>
+          <t>kWh</t>
         </is>
       </c>
       <c r="F1174" t="inlineStr">
         <is>
-          <t>capex_p</t>
+          <t>capex_e</t>
         </is>
       </c>
       <c r="G1174" t="inlineStr"/>
       <c r="H1174" t="inlineStr">
         <is>
-          <t>historic</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="I1174" t="inlineStr">
@@ -55518,18 +55524,14 @@
       <c r="J1174" t="n">
         <v>2025</v>
       </c>
-      <c r="K1174" t="inlineStr">
-        <is>
-          <t>IRENA 2024</t>
-        </is>
-      </c>
+      <c r="K1174" t="inlineStr"/>
     </row>
     <row r="1175">
       <c r="A1175" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B1175" t="n">
-        <v>4263.2</v>
+        <v>5142.8</v>
       </c>
       <c r="C1175" t="inlineStr">
         <is>
@@ -55573,10 +55575,10 @@
     </row>
     <row r="1176">
       <c r="A1176" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B1176" t="n">
-        <v>4020.4</v>
+        <v>4263.2</v>
       </c>
       <c r="C1176" t="inlineStr">
         <is>
@@ -55620,10 +55622,10 @@
     </row>
     <row r="1177">
       <c r="A1177" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B1177" t="n">
-        <v>3310</v>
+        <v>4020.4</v>
       </c>
       <c r="C1177" t="inlineStr">
         <is>
@@ -55667,10 +55669,10 @@
     </row>
     <row r="1178">
       <c r="A1178" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B1178" t="n">
-        <v>3483.2</v>
+        <v>3310</v>
       </c>
       <c r="C1178" t="inlineStr">
         <is>
@@ -55714,10 +55716,10 @@
     </row>
     <row r="1179">
       <c r="A1179" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B1179" t="n">
-        <v>3088</v>
+        <v>3483.2</v>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
@@ -55761,10 +55763,10 @@
     </row>
     <row r="1180">
       <c r="A1180" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B1180" t="n">
-        <v>2204</v>
+        <v>3088</v>
       </c>
       <c r="C1180" t="inlineStr">
         <is>
@@ -55808,10 +55810,10 @@
     </row>
     <row r="1181">
       <c r="A1181" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B1181" t="n">
-        <v>1579.4</v>
+        <v>2204</v>
       </c>
       <c r="C1181" t="inlineStr">
         <is>
@@ -55855,10 +55857,10 @@
     </row>
     <row r="1182">
       <c r="A1182" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B1182" t="n">
-        <v>1421.4</v>
+        <v>1579.4</v>
       </c>
       <c r="C1182" t="inlineStr">
         <is>
@@ -55902,10 +55904,10 @@
     </row>
     <row r="1183">
       <c r="A1183" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B1183" t="n">
-        <v>666.2</v>
+        <v>1421.4</v>
       </c>
       <c r="C1183" t="inlineStr">
         <is>
@@ -55949,10 +55951,10 @@
     </row>
     <row r="1184">
       <c r="A1184" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B1184" t="n">
-        <v>599.8</v>
+        <v>666.2</v>
       </c>
       <c r="C1184" t="inlineStr">
         <is>
@@ -55996,10 +55998,10 @@
     </row>
     <row r="1185">
       <c r="A1185" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B1185" t="n">
-        <v>563.6</v>
+        <v>599.8</v>
       </c>
       <c r="C1185" t="inlineStr">
         <is>
@@ -56043,10 +56045,10 @@
     </row>
     <row r="1186">
       <c r="A1186" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B1186" t="n">
-        <v>714</v>
+        <v>563.6</v>
       </c>
       <c r="C1186" t="inlineStr">
         <is>
@@ -56090,10 +56092,10 @@
     </row>
     <row r="1187">
       <c r="A1187" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B1187" t="n">
-        <v>543.6</v>
+        <v>714</v>
       </c>
       <c r="C1187" t="inlineStr">
         <is>
@@ -56137,10 +56139,10 @@
     </row>
     <row r="1188">
       <c r="A1188" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B1188" t="n">
-        <v>383.2</v>
+        <v>543.6</v>
       </c>
       <c r="C1188" t="inlineStr">
         <is>
@@ -56184,10 +56186,10 @@
     </row>
     <row r="1189">
       <c r="A1189" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B1189" t="n">
-        <v>323.6352331606217</v>
+        <v>383.2</v>
       </c>
       <c r="C1189" t="inlineStr">
         <is>
@@ -56212,7 +56214,7 @@
       <c r="G1189" t="inlineStr"/>
       <c r="H1189" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>historic</t>
         </is>
       </c>
       <c r="I1189" t="inlineStr">
@@ -56223,14 +56225,18 @@
       <c r="J1189" t="n">
         <v>2025</v>
       </c>
-      <c r="K1189" t="inlineStr"/>
+      <c r="K1189" t="inlineStr">
+        <is>
+          <t>IRENA 2024</t>
+        </is>
+      </c>
     </row>
     <row r="1190">
       <c r="A1190" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B1190" t="n">
-        <v>273.3</v>
+        <v>323.6352331606217</v>
       </c>
       <c r="C1190" t="inlineStr">
         <is>
@@ -56270,10 +56276,10 @@
     </row>
     <row r="1191">
       <c r="A1191" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B1191" t="n">
-        <v>208.8</v>
+        <v>273.3</v>
       </c>
       <c r="C1191" t="inlineStr">
         <is>
@@ -56313,10 +56319,10 @@
     </row>
     <row r="1192">
       <c r="A1192" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1192" t="n">
-        <v>189.5</v>
+        <v>208.8</v>
       </c>
       <c r="C1192" t="inlineStr">
         <is>
@@ -56356,10 +56362,10 @@
     </row>
     <row r="1193">
       <c r="A1193" t="n">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B1193" t="n">
-        <v>176.1</v>
+        <v>189.5</v>
       </c>
       <c r="C1193" t="inlineStr">
         <is>
@@ -56399,10 +56405,10 @@
     </row>
     <row r="1194">
       <c r="A1194" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B1194" t="n">
-        <v>167.7</v>
+        <v>176.1</v>
       </c>
       <c r="C1194" t="inlineStr">
         <is>
@@ -56442,10 +56448,10 @@
     </row>
     <row r="1195">
       <c r="A1195" t="n">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B1195" t="n">
-        <v>165.2</v>
+        <v>167.7</v>
       </c>
       <c r="C1195" t="inlineStr">
         <is>
@@ -56485,10 +56491,10 @@
     </row>
     <row r="1196">
       <c r="A1196" t="n">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B1196" t="n">
-        <v>162.7</v>
+        <v>165.2</v>
       </c>
       <c r="C1196" t="inlineStr">
         <is>
@@ -56528,10 +56534,10 @@
     </row>
     <row r="1197">
       <c r="A1197" t="n">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B1197" t="n">
-        <v>158.5</v>
+        <v>162.7</v>
       </c>
       <c r="C1197" t="inlineStr">
         <is>
@@ -56571,10 +56577,10 @@
     </row>
     <row r="1198">
       <c r="A1198" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B1198" t="n">
-        <v>155.9</v>
+        <v>158.5</v>
       </c>
       <c r="C1198" t="inlineStr">
         <is>
@@ -56614,10 +56620,10 @@
     </row>
     <row r="1199">
       <c r="A1199" t="n">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B1199" t="n">
-        <v>153.4</v>
+        <v>155.9</v>
       </c>
       <c r="C1199" t="inlineStr">
         <is>
@@ -56657,10 +56663,10 @@
     </row>
     <row r="1200">
       <c r="A1200" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B1200" t="n">
-        <v>154.3</v>
+        <v>153.4</v>
       </c>
       <c r="C1200" t="inlineStr">
         <is>
@@ -56700,10 +56706,10 @@
     </row>
     <row r="1201">
       <c r="A1201" t="n">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B1201" t="n">
-        <v>155.1</v>
+        <v>154.3</v>
       </c>
       <c r="C1201" t="inlineStr">
         <is>
@@ -56743,7 +56749,7 @@
     </row>
     <row r="1202">
       <c r="A1202" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B1202" t="n">
         <v>155.1</v>
@@ -56786,10 +56792,10 @@
     </row>
     <row r="1203">
       <c r="A1203" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B1203" t="n">
-        <v>155.9</v>
+        <v>155.1</v>
       </c>
       <c r="C1203" t="inlineStr">
         <is>
@@ -56829,10 +56835,10 @@
     </row>
     <row r="1204">
       <c r="A1204" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B1204" t="n">
-        <v>156.8</v>
+        <v>155.9</v>
       </c>
       <c r="C1204" t="inlineStr">
         <is>
@@ -56872,10 +56878,10 @@
     </row>
     <row r="1205">
       <c r="A1205" t="n">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B1205" t="n">
-        <v>157.6</v>
+        <v>156.8</v>
       </c>
       <c r="C1205" t="inlineStr">
         <is>
@@ -56915,7 +56921,7 @@
     </row>
     <row r="1206">
       <c r="A1206" t="n">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B1206" t="n">
         <v>157.6</v>
@@ -56958,7 +56964,7 @@
     </row>
     <row r="1207">
       <c r="A1207" t="n">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B1207" t="n">
         <v>157.6</v>
@@ -57001,10 +57007,10 @@
     </row>
     <row r="1208">
       <c r="A1208" t="n">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B1208" t="n">
-        <v>158.5</v>
+        <v>157.6</v>
       </c>
       <c r="C1208" t="inlineStr">
         <is>
@@ -57044,10 +57050,10 @@
     </row>
     <row r="1209">
       <c r="A1209" t="n">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B1209" t="n">
-        <v>157.6</v>
+        <v>158.5</v>
       </c>
       <c r="C1209" t="inlineStr">
         <is>
@@ -57087,10 +57093,10 @@
     </row>
     <row r="1210">
       <c r="A1210" t="n">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B1210" t="n">
-        <v>158.5</v>
+        <v>157.6</v>
       </c>
       <c r="C1210" t="inlineStr">
         <is>
@@ -57130,7 +57136,7 @@
     </row>
     <row r="1211">
       <c r="A1211" t="n">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B1211" t="n">
         <v>158.5</v>
@@ -57173,10 +57179,10 @@
     </row>
     <row r="1212">
       <c r="A1212" t="n">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B1212" t="n">
-        <v>157.6</v>
+        <v>158.5</v>
       </c>
       <c r="C1212" t="inlineStr">
         <is>
@@ -57216,7 +57222,7 @@
     </row>
     <row r="1213">
       <c r="A1213" t="n">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B1213" t="n">
         <v>157.6</v>
@@ -57258,13 +57264,11 @@
       <c r="K1213" t="inlineStr"/>
     </row>
     <row r="1214">
-      <c r="A1214" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
+      <c r="A1214" t="n">
+        <v>2049</v>
       </c>
       <c r="B1214" t="n">
-        <v>5.3</v>
+        <v>157.6</v>
       </c>
       <c r="C1214" t="inlineStr">
         <is>
@@ -57278,87 +57282,85 @@
       </c>
       <c r="E1214" t="inlineStr">
         <is>
-          <t>kWh/year</t>
+          <t>kW</t>
         </is>
       </c>
       <c r="F1214" t="inlineStr">
         <is>
-          <t>opex_f</t>
+          <t>capex_p</t>
         </is>
       </c>
       <c r="G1214" t="inlineStr"/>
       <c r="H1214" t="inlineStr">
         <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1214" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K1214" t="inlineStr"/>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B1215" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>kWh/year</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>opex_f</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr"/>
+      <c r="H1215" t="inlineStr">
+        <is>
           <t>historic</t>
         </is>
       </c>
-      <c r="I1214" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J1214" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K1214" t="inlineStr">
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1215" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K1215" t="inlineStr">
         <is>
           <t>Lazard 2024</t>
         </is>
       </c>
-    </row>
-    <row r="1215">
-      <c r="A1215" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B1215" t="n">
-        <v>85.63939393939394</v>
-      </c>
-      <c r="C1215" t="inlineStr">
-        <is>
-          <t>World</t>
-        </is>
-      </c>
-      <c r="D1215" t="inlineStr">
-        <is>
-          <t>BESS</t>
-        </is>
-      </c>
-      <c r="E1215" t="inlineStr">
-        <is>
-          <t>kWh</t>
-        </is>
-      </c>
-      <c r="F1215" t="inlineStr">
-        <is>
-          <t>capex_e</t>
-        </is>
-      </c>
-      <c r="G1215" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H1215" t="inlineStr">
-        <is>
-          <t>projected</t>
-        </is>
-      </c>
-      <c r="I1215" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J1215" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K1215" t="inlineStr"/>
     </row>
     <row r="1216">
       <c r="A1216" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B1216" t="n">
-        <v>76.59999999999999</v>
+        <v>85.63939393939394</v>
       </c>
       <c r="C1216" t="inlineStr">
         <is>
@@ -57402,10 +57404,10 @@
     </row>
     <row r="1217">
       <c r="A1217" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B1217" t="n">
-        <v>64.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="C1217" t="inlineStr">
         <is>
@@ -57449,10 +57451,10 @@
     </row>
     <row r="1218">
       <c r="A1218" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1218" t="n">
-        <v>61.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C1218" t="inlineStr">
         <is>
@@ -57496,10 +57498,10 @@
     </row>
     <row r="1219">
       <c r="A1219" t="n">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B1219" t="n">
-        <v>58.4</v>
+        <v>61.4</v>
       </c>
       <c r="C1219" t="inlineStr">
         <is>
@@ -57543,10 +57545,10 @@
     </row>
     <row r="1220">
       <c r="A1220" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B1220" t="n">
-        <v>57.1</v>
+        <v>58.4</v>
       </c>
       <c r="C1220" t="inlineStr">
         <is>
@@ -57590,10 +57592,10 @@
     </row>
     <row r="1221">
       <c r="A1221" t="n">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B1221" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="C1221" t="inlineStr">
         <is>
@@ -57637,10 +57639,10 @@
     </row>
     <row r="1222">
       <c r="A1222" t="n">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B1222" t="n">
-        <v>54.9</v>
+        <v>56.2</v>
       </c>
       <c r="C1222" t="inlineStr">
         <is>
@@ -57684,10 +57686,10 @@
     </row>
     <row r="1223">
       <c r="A1223" t="n">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B1223" t="n">
-        <v>54.5</v>
+        <v>54.9</v>
       </c>
       <c r="C1223" t="inlineStr">
         <is>
@@ -57731,10 +57733,10 @@
     </row>
     <row r="1224">
       <c r="A1224" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B1224" t="n">
-        <v>53.6</v>
+        <v>54.5</v>
       </c>
       <c r="C1224" t="inlineStr">
         <is>
@@ -57778,10 +57780,10 @@
     </row>
     <row r="1225">
       <c r="A1225" t="n">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B1225" t="n">
-        <v>52.8</v>
+        <v>53.6</v>
       </c>
       <c r="C1225" t="inlineStr">
         <is>
@@ -57825,7 +57827,7 @@
     </row>
     <row r="1226">
       <c r="A1226" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B1226" t="n">
         <v>52.8</v>
@@ -57872,7 +57874,7 @@
     </row>
     <row r="1227">
       <c r="A1227" t="n">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B1227" t="n">
         <v>52.8</v>
@@ -57919,7 +57921,7 @@
     </row>
     <row r="1228">
       <c r="A1228" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B1228" t="n">
         <v>52.8</v>
@@ -57966,10 +57968,10 @@
     </row>
     <row r="1229">
       <c r="A1229" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B1229" t="n">
-        <v>52.3</v>
+        <v>52.8</v>
       </c>
       <c r="C1229" t="inlineStr">
         <is>
@@ -58013,7 +58015,7 @@
     </row>
     <row r="1230">
       <c r="A1230" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B1230" t="n">
         <v>52.3</v>
@@ -58060,10 +58062,10 @@
     </row>
     <row r="1231">
       <c r="A1231" t="n">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B1231" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="C1231" t="inlineStr">
         <is>
@@ -58107,7 +58109,7 @@
     </row>
     <row r="1232">
       <c r="A1232" t="n">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B1232" t="n">
         <v>51.9</v>
@@ -58154,7 +58156,7 @@
     </row>
     <row r="1233">
       <c r="A1233" t="n">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B1233" t="n">
         <v>51.9</v>
@@ -58201,10 +58203,10 @@
     </row>
     <row r="1234">
       <c r="A1234" t="n">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B1234" t="n">
-        <v>51.5</v>
+        <v>51.9</v>
       </c>
       <c r="C1234" t="inlineStr">
         <is>
@@ -58248,7 +58250,7 @@
     </row>
     <row r="1235">
       <c r="A1235" t="n">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B1235" t="n">
         <v>51.5</v>
@@ -58295,10 +58297,10 @@
     </row>
     <row r="1236">
       <c r="A1236" t="n">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B1236" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="C1236" t="inlineStr">
         <is>
@@ -58342,10 +58344,10 @@
     </row>
     <row r="1237">
       <c r="A1237" t="n">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B1237" t="n">
-        <v>50.6</v>
+        <v>51</v>
       </c>
       <c r="C1237" t="inlineStr">
         <is>
@@ -58389,7 +58391,7 @@
     </row>
     <row r="1238">
       <c r="A1238" t="n">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B1238" t="n">
         <v>50.6</v>
@@ -58436,10 +58438,10 @@
     </row>
     <row r="1239">
       <c r="A1239" t="n">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B1239" t="n">
-        <v>50.2</v>
+        <v>50.6</v>
       </c>
       <c r="C1239" t="inlineStr">
         <is>
@@ -58483,10 +58485,10 @@
     </row>
     <row r="1240">
       <c r="A1240" t="n">
-        <v>2025</v>
+        <v>2049</v>
       </c>
       <c r="B1240" t="n">
-        <v>342.4974093264248</v>
+        <v>50.2</v>
       </c>
       <c r="C1240" t="inlineStr">
         <is>
@@ -58500,12 +58502,12 @@
       </c>
       <c r="E1240" t="inlineStr">
         <is>
-          <t>kW</t>
+          <t>kWh</t>
         </is>
       </c>
       <c r="F1240" t="inlineStr">
         <is>
-          <t>capex_p</t>
+          <t>capex_e</t>
         </is>
       </c>
       <c r="G1240" t="inlineStr">
@@ -58530,10 +58532,10 @@
     </row>
     <row r="1241">
       <c r="A1241" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B1241" t="n">
-        <v>306.1</v>
+        <v>342.4974093264248</v>
       </c>
       <c r="C1241" t="inlineStr">
         <is>
@@ -58577,10 +58579,10 @@
     </row>
     <row r="1242">
       <c r="A1242" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B1242" t="n">
-        <v>260</v>
+        <v>306.1</v>
       </c>
       <c r="C1242" t="inlineStr">
         <is>
@@ -58624,10 +58626,10 @@
     </row>
     <row r="1243">
       <c r="A1243" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B1243" t="n">
-        <v>244.9</v>
+        <v>260</v>
       </c>
       <c r="C1243" t="inlineStr">
         <is>
@@ -58671,10 +58673,10 @@
     </row>
     <row r="1244">
       <c r="A1244" t="n">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B1244" t="n">
-        <v>235.1</v>
+        <v>244.9</v>
       </c>
       <c r="C1244" t="inlineStr">
         <is>
@@ -58718,10 +58720,10 @@
     </row>
     <row r="1245">
       <c r="A1245" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B1245" t="n">
-        <v>227.1</v>
+        <v>235.1</v>
       </c>
       <c r="C1245" t="inlineStr">
         <is>
@@ -58765,10 +58767,10 @@
     </row>
     <row r="1246">
       <c r="A1246" t="n">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B1246" t="n">
-        <v>224.5</v>
+        <v>227.1</v>
       </c>
       <c r="C1246" t="inlineStr">
         <is>
@@ -58812,10 +58814,10 @@
     </row>
     <row r="1247">
       <c r="A1247" t="n">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B1247" t="n">
-        <v>222.7</v>
+        <v>224.5</v>
       </c>
       <c r="C1247" t="inlineStr">
         <is>
@@ -58859,10 +58861,10 @@
     </row>
     <row r="1248">
       <c r="A1248" t="n">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B1248" t="n">
-        <v>218.3</v>
+        <v>222.7</v>
       </c>
       <c r="C1248" t="inlineStr">
         <is>
@@ -58906,10 +58908,10 @@
     </row>
     <row r="1249">
       <c r="A1249" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B1249" t="n">
-        <v>215.6</v>
+        <v>218.3</v>
       </c>
       <c r="C1249" t="inlineStr">
         <is>
@@ -58953,10 +58955,10 @@
     </row>
     <row r="1250">
       <c r="A1250" t="n">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B1250" t="n">
-        <v>213</v>
+        <v>215.6</v>
       </c>
       <c r="C1250" t="inlineStr">
         <is>
@@ -59000,10 +59002,10 @@
     </row>
     <row r="1251">
       <c r="A1251" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B1251" t="n">
-        <v>212.1</v>
+        <v>213</v>
       </c>
       <c r="C1251" t="inlineStr">
         <is>
@@ -59047,10 +59049,10 @@
     </row>
     <row r="1252">
       <c r="A1252" t="n">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B1252" t="n">
-        <v>211.2</v>
+        <v>212.1</v>
       </c>
       <c r="C1252" t="inlineStr">
         <is>
@@ -59094,10 +59096,10 @@
     </row>
     <row r="1253">
       <c r="A1253" t="n">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B1253" t="n">
-        <v>210.3</v>
+        <v>211.2</v>
       </c>
       <c r="C1253" t="inlineStr">
         <is>
@@ -59141,7 +59143,7 @@
     </row>
     <row r="1254">
       <c r="A1254" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B1254" t="n">
         <v>210.3</v>
@@ -59188,10 +59190,10 @@
     </row>
     <row r="1255">
       <c r="A1255" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B1255" t="n">
-        <v>209.4</v>
+        <v>210.3</v>
       </c>
       <c r="C1255" t="inlineStr">
         <is>
@@ -59235,7 +59237,7 @@
     </row>
     <row r="1256">
       <c r="A1256" t="n">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B1256" t="n">
         <v>209.4</v>
@@ -59282,10 +59284,10 @@
     </row>
     <row r="1257">
       <c r="A1257" t="n">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B1257" t="n">
-        <v>208.5</v>
+        <v>209.4</v>
       </c>
       <c r="C1257" t="inlineStr">
         <is>
@@ -59329,10 +59331,10 @@
     </row>
     <row r="1258">
       <c r="A1258" t="n">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B1258" t="n">
-        <v>206.7</v>
+        <v>208.5</v>
       </c>
       <c r="C1258" t="inlineStr">
         <is>
@@ -59376,7 +59378,7 @@
     </row>
     <row r="1259">
       <c r="A1259" t="n">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B1259" t="n">
         <v>206.7</v>
@@ -59423,10 +59425,10 @@
     </row>
     <row r="1260">
       <c r="A1260" t="n">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B1260" t="n">
-        <v>205</v>
+        <v>206.7</v>
       </c>
       <c r="C1260" t="inlineStr">
         <is>
@@ -59470,7 +59472,7 @@
     </row>
     <row r="1261">
       <c r="A1261" t="n">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B1261" t="n">
         <v>205</v>
@@ -59517,10 +59519,10 @@
     </row>
     <row r="1262">
       <c r="A1262" t="n">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B1262" t="n">
-        <v>204.1</v>
+        <v>205</v>
       </c>
       <c r="C1262" t="inlineStr">
         <is>
@@ -59564,10 +59566,10 @@
     </row>
     <row r="1263">
       <c r="A1263" t="n">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B1263" t="n">
-        <v>202.3</v>
+        <v>204.1</v>
       </c>
       <c r="C1263" t="inlineStr">
         <is>
@@ -59611,101 +59613,97 @@
     </row>
     <row r="1264">
       <c r="A1264" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B1264" t="n">
+        <v>202.3</v>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>BESS</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>capex_p</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>projected</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1264" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K1264" t="inlineStr"/>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="n">
         <v>2049</v>
       </c>
-      <c r="B1264" t="n">
+      <c r="B1265" t="n">
         <v>201.4</v>
       </c>
-      <c r="C1264" t="inlineStr">
+      <c r="C1265" t="inlineStr">
         <is>
           <t>World</t>
         </is>
       </c>
-      <c r="D1264" t="inlineStr">
+      <c r="D1265" t="inlineStr">
         <is>
           <t>BESS</t>
         </is>
       </c>
-      <c r="E1264" t="inlineStr">
-        <is>
-          <t>kW</t>
-        </is>
-      </c>
-      <c r="F1264" t="inlineStr">
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
         <is>
           <t>capex_p</t>
         </is>
       </c>
-      <c r="G1264" t="inlineStr">
+      <c r="G1265" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H1264" t="inlineStr">
+      <c r="H1265" t="inlineStr">
         <is>
           <t>projected</t>
         </is>
       </c>
-      <c r="I1264" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J1264" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K1264" t="inlineStr"/>
-    </row>
-    <row r="1265">
-      <c r="A1265" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B1265" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C1265" t="inlineStr">
-        <is>
-          <t>Africa</t>
-        </is>
-      </c>
-      <c r="D1265" t="inlineStr">
-        <is>
-          <t>Solar</t>
-        </is>
-      </c>
-      <c r="E1265" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F1265" t="inlineStr">
-        <is>
-          <t>wacc</t>
-        </is>
-      </c>
-      <c r="G1265" t="inlineStr"/>
-      <c r="H1265" t="inlineStr">
-        <is>
-          <t>historic</t>
-        </is>
-      </c>
       <c r="I1265" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J1265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K1265" t="inlineStr">
-        <is>
-          <t>IRENA 2024</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1265" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K1265" t="inlineStr"/>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
@@ -59714,11 +59712,11 @@
         </is>
       </c>
       <c r="B1266" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="D1266" t="inlineStr">
@@ -59765,11 +59763,11 @@
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D1267" t="inlineStr">
@@ -59816,11 +59814,11 @@
         </is>
       </c>
       <c r="B1268" t="n">
-        <v>0.055</v>
+        <v>0.042</v>
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D1268" t="inlineStr">
@@ -59867,11 +59865,11 @@
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>0.077</v>
+        <v>0.055</v>
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
@@ -59918,11 +59916,11 @@
         </is>
       </c>
       <c r="B1270" t="n">
-        <v>0.039</v>
+        <v>0.077</v>
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>South America</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
@@ -59969,26 +59967,26 @@
         </is>
       </c>
       <c r="B1271" t="n">
-        <v>20</v>
+        <v>0.039</v>
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>World</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="E1271" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F1271" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>wacc</t>
         </is>
       </c>
       <c r="G1271" t="inlineStr"/>
@@ -60009,7 +60007,7 @@
       </c>
       <c r="K1271" t="inlineStr">
         <is>
-          <t>Lazard 2025</t>
+          <t>IRENA 2024</t>
         </is>
       </c>
     </row>
@@ -60020,7 +60018,7 @@
         </is>
       </c>
       <c r="B1272" t="n">
-        <v>0.57</v>
+        <v>20</v>
       </c>
       <c r="C1272" t="inlineStr">
         <is>
@@ -60034,18 +60032,18 @@
       </c>
       <c r="E1272" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="F1272" t="inlineStr">
         <is>
-          <t>efficiency</t>
+          <t>life</t>
         </is>
       </c>
       <c r="G1272" t="inlineStr"/>
       <c r="H1272" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>historic</t>
         </is>
       </c>
       <c r="I1272" t="inlineStr">
@@ -60060,7 +60058,7 @@
       </c>
       <c r="K1272" t="inlineStr">
         <is>
-          <t>GNESTE</t>
+          <t>Lazard 2025</t>
         </is>
       </c>
     </row>
@@ -60071,7 +60069,7 @@
         </is>
       </c>
       <c r="B1273" t="n">
-        <v>40</v>
+        <v>0.57</v>
       </c>
       <c r="C1273" t="inlineStr">
         <is>
@@ -60080,23 +60078,23 @@
       </c>
       <c r="D1273" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="E1273" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F1273" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>efficiency</t>
         </is>
       </c>
       <c r="G1273" t="inlineStr"/>
       <c r="H1273" t="inlineStr">
         <is>
-          <t>historic</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="I1273" t="inlineStr">
@@ -60111,7 +60109,7 @@
       </c>
       <c r="K1273" t="inlineStr">
         <is>
-          <t>Lazard 2025</t>
+          <t>GNESTE</t>
         </is>
       </c>
     </row>
@@ -60122,7 +60120,7 @@
         </is>
       </c>
       <c r="B1274" t="n">
-        <v>0.43</v>
+        <v>40</v>
       </c>
       <c r="C1274" t="inlineStr">
         <is>
@@ -60136,18 +60134,18 @@
       </c>
       <c r="E1274" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="F1274" t="inlineStr">
         <is>
-          <t>efficiency</t>
+          <t>life</t>
         </is>
       </c>
       <c r="G1274" t="inlineStr"/>
       <c r="H1274" t="inlineStr">
         <is>
-          <t>projected</t>
+          <t>historic</t>
         </is>
       </c>
       <c r="I1274" t="inlineStr">
@@ -60162,7 +60160,7 @@
       </c>
       <c r="K1274" t="inlineStr">
         <is>
-          <t>GNESTE</t>
+          <t>Lazard 2025</t>
         </is>
       </c>
     </row>
@@ -60173,7 +60171,7 @@
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>20</v>
+        <v>0.43</v>
       </c>
       <c r="C1275" t="inlineStr">
         <is>
@@ -60182,23 +60180,23 @@
       </c>
       <c r="D1275" t="inlineStr">
         <is>
-          <t>BESS</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="E1275" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F1275" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>efficiency</t>
         </is>
       </c>
       <c r="G1275" t="inlineStr"/>
       <c r="H1275" t="inlineStr">
         <is>
-          <t>historic</t>
+          <t>projected</t>
         </is>
       </c>
       <c r="I1275" t="inlineStr">
@@ -60213,7 +60211,7 @@
       </c>
       <c r="K1275" t="inlineStr">
         <is>
-          <t>Lazard 2025</t>
+          <t>GNESTE</t>
         </is>
       </c>
     </row>
@@ -60224,7 +60222,7 @@
         </is>
       </c>
       <c r="B1276" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C1276" t="inlineStr">
         <is>
@@ -60233,7 +60231,7 @@
       </c>
       <c r="D1276" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>BESS</t>
         </is>
       </c>
       <c r="E1276" t="inlineStr">
@@ -60275,7 +60273,7 @@
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C1277" t="inlineStr">
         <is>
@@ -60284,7 +60282,7 @@
       </c>
       <c r="D1277" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="E1277" t="inlineStr">
@@ -60314,6 +60312,57 @@
         </is>
       </c>
       <c r="K1277" t="inlineStr">
+        <is>
+          <t>Lazard 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B1278" t="n">
+        <v>70</v>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>life</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr"/>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>historic</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J1278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K1278" t="inlineStr">
         <is>
           <t>Lazard 2025</t>
         </is>
